--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/05 Mayo/Liquidacióncvs - VENTAS - CONDICIONAL SABA/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_6B7902D85257D20E62355476585DCE3A87478B38" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B975553-0320-45FD-BE91-9C7A6C68B0D2}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_6B7902D85257D20E62355476585DCE3A87478B38" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40C03C10-59A8-4053-9A80-0118191228DD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="112">
   <si>
     <t>Producto</t>
   </si>
@@ -170,25 +170,205 @@
   </si>
   <si>
     <t>39%</t>
+  </si>
+  <si>
+    <t>LA ESTRELLA</t>
+  </si>
+  <si>
+    <t>17%</t>
+  </si>
+  <si>
+    <t>22%</t>
+  </si>
+  <si>
+    <t>Yessica  Restrepo Caicedo</t>
+  </si>
+  <si>
+    <t>Meta 33</t>
+  </si>
+  <si>
+    <t>62%</t>
+  </si>
+  <si>
+    <t>Meta 14</t>
+  </si>
+  <si>
+    <t>89%</t>
+  </si>
+  <si>
+    <t>Meta  4</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>LÃ­der Estrella Milton Hernando Barrera Castro</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>ITAGUI</t>
+  </si>
+  <si>
+    <t>Jhon Alejandro Cardona Quintero</t>
+  </si>
+  <si>
+    <t>124%</t>
+  </si>
+  <si>
+    <t>93%</t>
+  </si>
+  <si>
+    <t>150%</t>
+  </si>
+  <si>
+    <t>El 19 pasa a Capacitación como líder para el CVS de la Estrella</t>
+  </si>
+  <si>
+    <t>Dailyn Del Valle Alvarez Rueda</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>Lider Marcela Valencia Tabares</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>112%</t>
+  </si>
+  <si>
+    <t>Incp 5 días -Meta puntos 712.5     meta post  7</t>
+  </si>
+  <si>
+    <t>Le finalizaron contrato el 15</t>
+  </si>
+  <si>
+    <t>COPACABANA</t>
+  </si>
+  <si>
+    <t>Bibiana Farley Rios Agudelo</t>
+  </si>
+  <si>
+    <t>Ingresa de vacaciones el 21</t>
+  </si>
+  <si>
+    <t>138%</t>
+  </si>
+  <si>
+    <t>Alexandra Patricia Duque</t>
+  </si>
+  <si>
+    <t>81%</t>
+  </si>
+  <si>
+    <t>98%</t>
+  </si>
+  <si>
+    <t>171%</t>
+  </si>
+  <si>
+    <t>118%</t>
+  </si>
+  <si>
+    <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+  </si>
+  <si>
+    <t>94%</t>
+  </si>
+  <si>
+    <t>120%</t>
+  </si>
+  <si>
+    <t>111%</t>
+  </si>
+  <si>
+    <t>BARBOSA</t>
+  </si>
+  <si>
+    <t>2%</t>
+  </si>
+  <si>
+    <t>5%</t>
+  </si>
+  <si>
+    <t>Evelis Mary Ojeda Baldovino</t>
+  </si>
+  <si>
+    <t>7%</t>
+  </si>
+  <si>
+    <t>Nueva- ingresa el 23 aplica mes de gracia en el mes de Junio</t>
+  </si>
+  <si>
+    <t>6%</t>
+  </si>
+  <si>
+    <t>Sene Del Socorro Suarez Torres</t>
+  </si>
+  <si>
+    <t>105%</t>
+  </si>
+  <si>
+    <t>83%</t>
+  </si>
+  <si>
+    <t>117%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
+  </si>
+  <si>
+    <t>145%</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Posada Galeano</t>
+  </si>
+  <si>
+    <t>Nueva inicia el 15 - mes de gracia hasta el 15 de junio</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>103%</t>
+  </si>
+  <si>
+    <t>157%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>65%</t>
+  </si>
+  <si>
+    <t>45%</t>
+  </si>
+  <si>
+    <t>90%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -199,7 +379,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -207,30 +387,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -541,40 +703,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1463,6 +1625,2833 @@
       </c>
       <c r="L26">
         <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27">
+        <v>20</v>
+      </c>
+      <c r="C27">
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" t="s">
+        <v>36</v>
+      </c>
+      <c r="I27" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27">
+        <v>100</v>
+      </c>
+      <c r="L27">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" t="s">
+        <v>36</v>
+      </c>
+      <c r="I28" t="s">
+        <v>16</v>
+      </c>
+      <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29">
+        <v>20</v>
+      </c>
+      <c r="C29">
+        <v>9</v>
+      </c>
+      <c r="D29" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" t="s">
+        <v>16</v>
+      </c>
+      <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30">
+        <v>69</v>
+      </c>
+      <c r="C30">
+        <v>45</v>
+      </c>
+      <c r="D30" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31">
+        <v>491</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" t="s">
+        <v>108</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32">
+        <v>30</v>
+      </c>
+      <c r="C32">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" t="s">
+        <v>102</v>
+      </c>
+      <c r="H32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
+        <v>100.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" t="s">
+        <v>105</v>
+      </c>
+      <c r="F33" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" t="s">
+        <v>102</v>
+      </c>
+      <c r="H33" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="L33">
+        <v>100.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34">
+        <v>29</v>
+      </c>
+      <c r="C34">
+        <v>30</v>
+      </c>
+      <c r="D34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34">
+        <v>100</v>
+      </c>
+      <c r="L34">
+        <v>100.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>109</v>
+      </c>
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
+        <v>100.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36">
+        <v>731</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" t="s">
+        <v>105</v>
+      </c>
+      <c r="F36" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" t="s">
+        <v>102</v>
+      </c>
+      <c r="H36" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" t="s">
+        <v>16</v>
+      </c>
+      <c r="K36">
+        <v>100</v>
+      </c>
+      <c r="L36">
+        <v>100.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37">
+        <v>12</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" t="s">
+        <v>102</v>
+      </c>
+      <c r="H37" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" t="s">
+        <v>104</v>
+      </c>
+      <c r="K37">
+        <v>100</v>
+      </c>
+      <c r="L37">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" t="s">
+        <v>103</v>
+      </c>
+      <c r="F38" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38" t="s">
+        <v>36</v>
+      </c>
+      <c r="I38" t="s">
+        <v>16</v>
+      </c>
+      <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39">
+        <v>11</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" t="s">
+        <v>103</v>
+      </c>
+      <c r="F39" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" t="s">
+        <v>102</v>
+      </c>
+      <c r="H39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" t="s">
+        <v>16</v>
+      </c>
+      <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40">
+        <v>39</v>
+      </c>
+      <c r="C40">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s">
+        <v>70</v>
+      </c>
+      <c r="E40" t="s">
+        <v>103</v>
+      </c>
+      <c r="F40" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" t="s">
+        <v>102</v>
+      </c>
+      <c r="H40" t="s">
+        <v>36</v>
+      </c>
+      <c r="I40" t="s">
+        <v>16</v>
+      </c>
+      <c r="K40">
+        <v>100</v>
+      </c>
+      <c r="L40">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41">
+        <v>281</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" t="s">
+        <v>103</v>
+      </c>
+      <c r="F41" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" t="s">
+        <v>102</v>
+      </c>
+      <c r="H41" t="s">
+        <v>36</v>
+      </c>
+      <c r="I41" t="s">
+        <v>16</v>
+      </c>
+      <c r="K41">
+        <v>100</v>
+      </c>
+      <c r="L41">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42">
+        <v>12</v>
+      </c>
+      <c r="C42">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" t="s">
+        <v>100</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" t="s">
+        <v>89</v>
+      </c>
+      <c r="H42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" t="s">
+        <v>16</v>
+      </c>
+      <c r="K42">
+        <v>100</v>
+      </c>
+      <c r="L42">
+        <v>96.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" t="s">
+        <v>100</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>89</v>
+      </c>
+      <c r="H43" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" t="s">
+        <v>16</v>
+      </c>
+      <c r="K43">
+        <v>100</v>
+      </c>
+      <c r="L43">
+        <v>96.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44">
+        <v>29</v>
+      </c>
+      <c r="C44">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" t="s">
+        <v>100</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s">
+        <v>89</v>
+      </c>
+      <c r="H44" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" t="s">
+        <v>16</v>
+      </c>
+      <c r="K44">
+        <v>100</v>
+      </c>
+      <c r="L44">
+        <v>96.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45">
+        <v>38</v>
+      </c>
+      <c r="C45">
+        <v>55</v>
+      </c>
+      <c r="D45" t="s">
+        <v>101</v>
+      </c>
+      <c r="E45" t="s">
+        <v>100</v>
+      </c>
+      <c r="F45" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" t="s">
+        <v>89</v>
+      </c>
+      <c r="H45" t="s">
+        <v>36</v>
+      </c>
+      <c r="I45" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45">
+        <v>100</v>
+      </c>
+      <c r="L45">
+        <v>96.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46">
+        <v>600</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" t="s">
+        <v>100</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" t="s">
+        <v>89</v>
+      </c>
+      <c r="H46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" t="s">
+        <v>16</v>
+      </c>
+      <c r="K46">
+        <v>100</v>
+      </c>
+      <c r="L46">
+        <v>96.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47">
+        <v>18</v>
+      </c>
+      <c r="C47">
+        <v>21</v>
+      </c>
+      <c r="D47" t="s">
+        <v>99</v>
+      </c>
+      <c r="E47" t="s">
+        <v>96</v>
+      </c>
+      <c r="F47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" t="s">
+        <v>89</v>
+      </c>
+      <c r="H47" t="s">
+        <v>36</v>
+      </c>
+      <c r="I47" t="s">
+        <v>16</v>
+      </c>
+      <c r="K47">
+        <v>100</v>
+      </c>
+      <c r="L47">
+        <v>107.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48">
+        <v>6</v>
+      </c>
+      <c r="C48">
+        <v>5</v>
+      </c>
+      <c r="D48" t="s">
+        <v>98</v>
+      </c>
+      <c r="E48" t="s">
+        <v>96</v>
+      </c>
+      <c r="F48" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" t="s">
+        <v>89</v>
+      </c>
+      <c r="H48" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48">
+        <v>100</v>
+      </c>
+      <c r="L48">
+        <v>107.1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49">
+        <v>43</v>
+      </c>
+      <c r="C49">
+        <v>44</v>
+      </c>
+      <c r="D49" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" t="s">
+        <v>96</v>
+      </c>
+      <c r="F49" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" t="s">
+        <v>89</v>
+      </c>
+      <c r="H49" t="s">
+        <v>36</v>
+      </c>
+      <c r="I49" t="s">
+        <v>16</v>
+      </c>
+      <c r="K49">
+        <v>100</v>
+      </c>
+      <c r="L49">
+        <v>107.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50">
+        <v>57</v>
+      </c>
+      <c r="C50">
+        <v>60</v>
+      </c>
+      <c r="D50" t="s">
+        <v>97</v>
+      </c>
+      <c r="E50" t="s">
+        <v>96</v>
+      </c>
+      <c r="F50" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" t="s">
+        <v>89</v>
+      </c>
+      <c r="H50" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" t="s">
+        <v>16</v>
+      </c>
+      <c r="K50">
+        <v>100</v>
+      </c>
+      <c r="L50">
+        <v>107.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51">
+        <v>900</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" t="s">
+        <v>96</v>
+      </c>
+      <c r="F51" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" t="s">
+        <v>89</v>
+      </c>
+      <c r="H51" t="s">
+        <v>36</v>
+      </c>
+      <c r="I51" t="s">
+        <v>16</v>
+      </c>
+      <c r="K51">
+        <v>100</v>
+      </c>
+      <c r="L51">
+        <v>107.1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52">
+        <v>18</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" t="s">
+        <v>92</v>
+      </c>
+      <c r="F52" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" t="s">
+        <v>89</v>
+      </c>
+      <c r="H52" t="s">
+        <v>36</v>
+      </c>
+      <c r="I52" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" t="s">
+        <v>94</v>
+      </c>
+      <c r="K52">
+        <v>100</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53">
+        <v>6</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" t="s">
+        <v>92</v>
+      </c>
+      <c r="F53" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" t="s">
+        <v>89</v>
+      </c>
+      <c r="H53" t="s">
+        <v>36</v>
+      </c>
+      <c r="I53" t="s">
+        <v>16</v>
+      </c>
+      <c r="K53">
+        <v>100</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54">
+        <v>43</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" t="s">
+        <v>89</v>
+      </c>
+      <c r="H54" t="s">
+        <v>36</v>
+      </c>
+      <c r="I54" t="s">
+        <v>16</v>
+      </c>
+      <c r="K54">
+        <v>100</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55">
+        <v>57</v>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>93</v>
+      </c>
+      <c r="E55" t="s">
+        <v>92</v>
+      </c>
+      <c r="F55" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" t="s">
+        <v>89</v>
+      </c>
+      <c r="H55" t="s">
+        <v>36</v>
+      </c>
+      <c r="I55" t="s">
+        <v>16</v>
+      </c>
+      <c r="K55">
+        <v>100</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56">
+        <v>900</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" t="s">
+        <v>92</v>
+      </c>
+      <c r="F56" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" t="s">
+        <v>89</v>
+      </c>
+      <c r="H56" t="s">
+        <v>36</v>
+      </c>
+      <c r="I56" t="s">
+        <v>16</v>
+      </c>
+      <c r="K56">
+        <v>100</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57">
+        <v>18</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" t="s">
+        <v>31</v>
+      </c>
+      <c r="F57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" t="s">
+        <v>89</v>
+      </c>
+      <c r="H57" t="s">
+        <v>36</v>
+      </c>
+      <c r="I57" t="s">
+        <v>16</v>
+      </c>
+      <c r="K57">
+        <v>100</v>
+      </c>
+      <c r="L57">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" t="s">
+        <v>31</v>
+      </c>
+      <c r="F58" t="s">
+        <v>24</v>
+      </c>
+      <c r="G58" t="s">
+        <v>89</v>
+      </c>
+      <c r="H58" t="s">
+        <v>36</v>
+      </c>
+      <c r="I58" t="s">
+        <v>16</v>
+      </c>
+      <c r="K58">
+        <v>100</v>
+      </c>
+      <c r="L58">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59">
+        <v>43</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59" t="s">
+        <v>91</v>
+      </c>
+      <c r="E59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F59" t="s">
+        <v>24</v>
+      </c>
+      <c r="G59" t="s">
+        <v>89</v>
+      </c>
+      <c r="H59" t="s">
+        <v>36</v>
+      </c>
+      <c r="I59" t="s">
+        <v>16</v>
+      </c>
+      <c r="K59">
+        <v>100</v>
+      </c>
+      <c r="L59">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60">
+        <v>57</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60" t="s">
+        <v>90</v>
+      </c>
+      <c r="E60" t="s">
+        <v>31</v>
+      </c>
+      <c r="F60" t="s">
+        <v>24</v>
+      </c>
+      <c r="G60" t="s">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s">
+        <v>36</v>
+      </c>
+      <c r="I60" t="s">
+        <v>16</v>
+      </c>
+      <c r="K60">
+        <v>100</v>
+      </c>
+      <c r="L60">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61">
+        <v>900</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" t="s">
+        <v>31</v>
+      </c>
+      <c r="F61" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" t="s">
+        <v>89</v>
+      </c>
+      <c r="H61" t="s">
+        <v>36</v>
+      </c>
+      <c r="I61" t="s">
+        <v>16</v>
+      </c>
+      <c r="K61">
+        <v>100</v>
+      </c>
+      <c r="L61">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62">
+        <v>19</v>
+      </c>
+      <c r="C62">
+        <v>21</v>
+      </c>
+      <c r="D62" t="s">
+        <v>88</v>
+      </c>
+      <c r="E62" t="s">
+        <v>85</v>
+      </c>
+      <c r="F62" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" t="s">
+        <v>76</v>
+      </c>
+      <c r="H62" t="s">
+        <v>36</v>
+      </c>
+      <c r="I62" t="s">
+        <v>16</v>
+      </c>
+      <c r="K62">
+        <v>100</v>
+      </c>
+      <c r="L62">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B63">
+        <v>5</v>
+      </c>
+      <c r="C63">
+        <v>6</v>
+      </c>
+      <c r="D63" t="s">
+        <v>87</v>
+      </c>
+      <c r="E63" t="s">
+        <v>85</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H63" t="s">
+        <v>36</v>
+      </c>
+      <c r="I63" t="s">
+        <v>16</v>
+      </c>
+      <c r="K63">
+        <v>100</v>
+      </c>
+      <c r="L63">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64">
+        <v>33</v>
+      </c>
+      <c r="C64">
+        <v>33</v>
+      </c>
+      <c r="D64" t="s">
+        <v>33</v>
+      </c>
+      <c r="E64" t="s">
+        <v>85</v>
+      </c>
+      <c r="F64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" t="s">
+        <v>76</v>
+      </c>
+      <c r="H64" t="s">
+        <v>36</v>
+      </c>
+      <c r="I64" t="s">
+        <v>16</v>
+      </c>
+      <c r="K64">
+        <v>100</v>
+      </c>
+      <c r="L64">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65">
+        <v>62</v>
+      </c>
+      <c r="C65">
+        <v>58</v>
+      </c>
+      <c r="D65" t="s">
+        <v>86</v>
+      </c>
+      <c r="E65" t="s">
+        <v>85</v>
+      </c>
+      <c r="F65" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" t="s">
+        <v>76</v>
+      </c>
+      <c r="H65" t="s">
+        <v>36</v>
+      </c>
+      <c r="I65" t="s">
+        <v>16</v>
+      </c>
+      <c r="K65">
+        <v>100</v>
+      </c>
+      <c r="L65">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>20</v>
+      </c>
+      <c r="B66">
+        <v>516</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66" t="s">
+        <v>85</v>
+      </c>
+      <c r="F66" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" t="s">
+        <v>76</v>
+      </c>
+      <c r="H66" t="s">
+        <v>36</v>
+      </c>
+      <c r="I66" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66">
+        <v>100</v>
+      </c>
+      <c r="L66">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67">
+        <v>28</v>
+      </c>
+      <c r="C67">
+        <v>33</v>
+      </c>
+      <c r="D67" t="s">
+        <v>84</v>
+      </c>
+      <c r="E67" t="s">
+        <v>80</v>
+      </c>
+      <c r="F67" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" t="s">
+        <v>76</v>
+      </c>
+      <c r="H67" t="s">
+        <v>36</v>
+      </c>
+      <c r="I67" t="s">
+        <v>16</v>
+      </c>
+      <c r="K67">
+        <v>100</v>
+      </c>
+      <c r="L67">
+        <v>110.2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>17</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68">
+        <v>12</v>
+      </c>
+      <c r="D68" t="s">
+        <v>83</v>
+      </c>
+      <c r="E68" t="s">
+        <v>80</v>
+      </c>
+      <c r="F68" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68" t="s">
+        <v>76</v>
+      </c>
+      <c r="H68" t="s">
+        <v>36</v>
+      </c>
+      <c r="I68" t="s">
+        <v>16</v>
+      </c>
+      <c r="K68">
+        <v>100</v>
+      </c>
+      <c r="L68">
+        <v>110.2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69">
+        <v>49</v>
+      </c>
+      <c r="C69">
+        <v>48</v>
+      </c>
+      <c r="D69" t="s">
+        <v>82</v>
+      </c>
+      <c r="E69" t="s">
+        <v>80</v>
+      </c>
+      <c r="F69" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" t="s">
+        <v>76</v>
+      </c>
+      <c r="H69" t="s">
+        <v>36</v>
+      </c>
+      <c r="I69" t="s">
+        <v>16</v>
+      </c>
+      <c r="K69">
+        <v>100</v>
+      </c>
+      <c r="L69">
+        <v>110.2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70">
+        <v>93</v>
+      </c>
+      <c r="C70">
+        <v>75</v>
+      </c>
+      <c r="D70" t="s">
+        <v>81</v>
+      </c>
+      <c r="E70" t="s">
+        <v>80</v>
+      </c>
+      <c r="F70" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" t="s">
+        <v>76</v>
+      </c>
+      <c r="H70" t="s">
+        <v>36</v>
+      </c>
+      <c r="I70" t="s">
+        <v>16</v>
+      </c>
+      <c r="K70">
+        <v>100</v>
+      </c>
+      <c r="L70">
+        <v>110.2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>20</v>
+      </c>
+      <c r="B71">
+        <v>774</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71" t="s">
+        <v>80</v>
+      </c>
+      <c r="F71" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" t="s">
+        <v>76</v>
+      </c>
+      <c r="H71" t="s">
+        <v>36</v>
+      </c>
+      <c r="I71" t="s">
+        <v>16</v>
+      </c>
+      <c r="K71">
+        <v>100</v>
+      </c>
+      <c r="L71">
+        <v>110.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72">
+        <v>8</v>
+      </c>
+      <c r="C72">
+        <v>11</v>
+      </c>
+      <c r="D72" t="s">
+        <v>79</v>
+      </c>
+      <c r="E72" t="s">
+        <v>77</v>
+      </c>
+      <c r="F72" t="s">
+        <v>23</v>
+      </c>
+      <c r="G72" t="s">
+        <v>76</v>
+      </c>
+      <c r="H72" t="s">
+        <v>36</v>
+      </c>
+      <c r="I72" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" t="s">
+        <v>78</v>
+      </c>
+      <c r="K72">
+        <v>100</v>
+      </c>
+      <c r="L72">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="D73" t="s">
+        <v>33</v>
+      </c>
+      <c r="E73" t="s">
+        <v>77</v>
+      </c>
+      <c r="F73" t="s">
+        <v>23</v>
+      </c>
+      <c r="G73" t="s">
+        <v>76</v>
+      </c>
+      <c r="H73" t="s">
+        <v>36</v>
+      </c>
+      <c r="I73" t="s">
+        <v>16</v>
+      </c>
+      <c r="K73">
+        <v>100</v>
+      </c>
+      <c r="L73">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B74">
+        <v>13</v>
+      </c>
+      <c r="C74">
+        <v>12</v>
+      </c>
+      <c r="D74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" t="s">
+        <v>77</v>
+      </c>
+      <c r="F74" t="s">
+        <v>23</v>
+      </c>
+      <c r="G74" t="s">
+        <v>76</v>
+      </c>
+      <c r="H74" t="s">
+        <v>36</v>
+      </c>
+      <c r="I74" t="s">
+        <v>16</v>
+      </c>
+      <c r="K74">
+        <v>100</v>
+      </c>
+      <c r="L74">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>19</v>
+      </c>
+      <c r="B75">
+        <v>25</v>
+      </c>
+      <c r="C75">
+        <v>28</v>
+      </c>
+      <c r="D75" t="s">
+        <v>73</v>
+      </c>
+      <c r="E75" t="s">
+        <v>77</v>
+      </c>
+      <c r="F75" t="s">
+        <v>23</v>
+      </c>
+      <c r="G75" t="s">
+        <v>76</v>
+      </c>
+      <c r="H75" t="s">
+        <v>36</v>
+      </c>
+      <c r="I75" t="s">
+        <v>16</v>
+      </c>
+      <c r="K75">
+        <v>100</v>
+      </c>
+      <c r="L75">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>20</v>
+      </c>
+      <c r="B76">
+        <v>211</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" t="s">
+        <v>77</v>
+      </c>
+      <c r="F76" t="s">
+        <v>23</v>
+      </c>
+      <c r="G76" t="s">
+        <v>76</v>
+      </c>
+      <c r="H76" t="s">
+        <v>36</v>
+      </c>
+      <c r="I76" t="s">
+        <v>16</v>
+      </c>
+      <c r="K76">
+        <v>100</v>
+      </c>
+      <c r="L76">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>3</v>
+      </c>
+      <c r="D77" t="s">
+        <v>61</v>
+      </c>
+      <c r="E77" t="s">
+        <v>60</v>
+      </c>
+      <c r="F77" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>50</v>
+      </c>
+      <c r="H77" t="s">
+        <v>36</v>
+      </c>
+      <c r="I77" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" t="s">
+        <v>75</v>
+      </c>
+      <c r="K77">
+        <v>100</v>
+      </c>
+      <c r="L77">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78">
+        <v>3</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78" t="s">
+        <v>21</v>
+      </c>
+      <c r="E78" t="s">
+        <v>60</v>
+      </c>
+      <c r="F78" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" t="s">
+        <v>50</v>
+      </c>
+      <c r="H78" t="s">
+        <v>36</v>
+      </c>
+      <c r="I78" t="s">
+        <v>16</v>
+      </c>
+      <c r="K78">
+        <v>100</v>
+      </c>
+      <c r="L78">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>18</v>
+      </c>
+      <c r="B79">
+        <v>12</v>
+      </c>
+      <c r="C79">
+        <v>5</v>
+      </c>
+      <c r="D79" t="s">
+        <v>32</v>
+      </c>
+      <c r="E79" t="s">
+        <v>60</v>
+      </c>
+      <c r="F79" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s">
+        <v>50</v>
+      </c>
+      <c r="H79" t="s">
+        <v>36</v>
+      </c>
+      <c r="I79" t="s">
+        <v>16</v>
+      </c>
+      <c r="K79">
+        <v>100</v>
+      </c>
+      <c r="L79">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>19</v>
+      </c>
+      <c r="B80">
+        <v>28</v>
+      </c>
+      <c r="C80">
+        <v>8</v>
+      </c>
+      <c r="D80" t="s">
+        <v>41</v>
+      </c>
+      <c r="E80" t="s">
+        <v>60</v>
+      </c>
+      <c r="F80" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" t="s">
+        <v>50</v>
+      </c>
+      <c r="H80" t="s">
+        <v>36</v>
+      </c>
+      <c r="I80" t="s">
+        <v>16</v>
+      </c>
+      <c r="K80">
+        <v>100</v>
+      </c>
+      <c r="L80">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>20</v>
+      </c>
+      <c r="B81">
+        <v>480</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81" t="s">
+        <v>21</v>
+      </c>
+      <c r="E81" t="s">
+        <v>60</v>
+      </c>
+      <c r="F81" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" t="s">
+        <v>50</v>
+      </c>
+      <c r="H81" t="s">
+        <v>36</v>
+      </c>
+      <c r="I81" t="s">
+        <v>16</v>
+      </c>
+      <c r="K81">
+        <v>100</v>
+      </c>
+      <c r="L81">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82">
+        <v>9</v>
+      </c>
+      <c r="C82">
+        <v>8</v>
+      </c>
+      <c r="D82" t="s">
+        <v>57</v>
+      </c>
+      <c r="E82" t="s">
+        <v>53</v>
+      </c>
+      <c r="F82" t="s">
+        <v>23</v>
+      </c>
+      <c r="G82" t="s">
+        <v>50</v>
+      </c>
+      <c r="H82" t="s">
+        <v>36</v>
+      </c>
+      <c r="I82" t="s">
+        <v>16</v>
+      </c>
+      <c r="J82" t="s">
+        <v>74</v>
+      </c>
+      <c r="K82">
+        <v>100</v>
+      </c>
+      <c r="L82">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B83">
+        <v>5</v>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83" t="s">
+        <v>59</v>
+      </c>
+      <c r="E83" t="s">
+        <v>53</v>
+      </c>
+      <c r="F83" t="s">
+        <v>23</v>
+      </c>
+      <c r="G83" t="s">
+        <v>50</v>
+      </c>
+      <c r="H83" t="s">
+        <v>36</v>
+      </c>
+      <c r="I83" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" t="s">
+        <v>58</v>
+      </c>
+      <c r="K83">
+        <v>100</v>
+      </c>
+      <c r="L83">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>18</v>
+      </c>
+      <c r="B84">
+        <v>18</v>
+      </c>
+      <c r="C84">
+        <v>16</v>
+      </c>
+      <c r="D84" t="s">
+        <v>57</v>
+      </c>
+      <c r="E84" t="s">
+        <v>53</v>
+      </c>
+      <c r="F84" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" t="s">
+        <v>50</v>
+      </c>
+      <c r="H84" t="s">
+        <v>36</v>
+      </c>
+      <c r="I84" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" t="s">
+        <v>56</v>
+      </c>
+      <c r="K84">
+        <v>100</v>
+      </c>
+      <c r="L84">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85">
+        <v>42</v>
+      </c>
+      <c r="C85">
+        <v>26</v>
+      </c>
+      <c r="D85" t="s">
+        <v>55</v>
+      </c>
+      <c r="E85" t="s">
+        <v>53</v>
+      </c>
+      <c r="F85" t="s">
+        <v>23</v>
+      </c>
+      <c r="G85" t="s">
+        <v>50</v>
+      </c>
+      <c r="H85" t="s">
+        <v>36</v>
+      </c>
+      <c r="I85" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" t="s">
+        <v>54</v>
+      </c>
+      <c r="K85">
+        <v>100</v>
+      </c>
+      <c r="L85">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>20</v>
+      </c>
+      <c r="B86">
+        <v>720</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86" t="s">
+        <v>21</v>
+      </c>
+      <c r="E86" t="s">
+        <v>53</v>
+      </c>
+      <c r="F86" t="s">
+        <v>23</v>
+      </c>
+      <c r="G86" t="s">
+        <v>50</v>
+      </c>
+      <c r="H86" t="s">
+        <v>36</v>
+      </c>
+      <c r="I86" t="s">
+        <v>16</v>
+      </c>
+      <c r="K86">
+        <v>100</v>
+      </c>
+      <c r="L86">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B87">
+        <v>9</v>
+      </c>
+      <c r="C87">
+        <v>6</v>
+      </c>
+      <c r="D87" t="s">
+        <v>30</v>
+      </c>
+      <c r="E87" t="s">
+        <v>31</v>
+      </c>
+      <c r="F87" t="s">
+        <v>24</v>
+      </c>
+      <c r="G87" t="s">
+        <v>50</v>
+      </c>
+      <c r="H87" t="s">
+        <v>36</v>
+      </c>
+      <c r="I87" t="s">
+        <v>16</v>
+      </c>
+      <c r="K87">
+        <v>100</v>
+      </c>
+      <c r="L87">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>17</v>
+      </c>
+      <c r="B88">
+        <v>5</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88" t="s">
+        <v>21</v>
+      </c>
+      <c r="E88" t="s">
+        <v>31</v>
+      </c>
+      <c r="F88" t="s">
+        <v>24</v>
+      </c>
+      <c r="G88" t="s">
+        <v>50</v>
+      </c>
+      <c r="H88" t="s">
+        <v>36</v>
+      </c>
+      <c r="I88" t="s">
+        <v>16</v>
+      </c>
+      <c r="K88">
+        <v>100</v>
+      </c>
+      <c r="L88">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>18</v>
+      </c>
+      <c r="B89">
+        <v>18</v>
+      </c>
+      <c r="C89">
+        <v>4</v>
+      </c>
+      <c r="D89" t="s">
+        <v>52</v>
+      </c>
+      <c r="E89" t="s">
+        <v>31</v>
+      </c>
+      <c r="F89" t="s">
+        <v>24</v>
+      </c>
+      <c r="G89" t="s">
+        <v>50</v>
+      </c>
+      <c r="H89" t="s">
+        <v>36</v>
+      </c>
+      <c r="I89" t="s">
+        <v>16</v>
+      </c>
+      <c r="K89">
+        <v>100</v>
+      </c>
+      <c r="L89">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>19</v>
+      </c>
+      <c r="B90">
+        <v>42</v>
+      </c>
+      <c r="C90">
+        <v>7</v>
+      </c>
+      <c r="D90" t="s">
+        <v>51</v>
+      </c>
+      <c r="E90" t="s">
+        <v>31</v>
+      </c>
+      <c r="F90" t="s">
+        <v>24</v>
+      </c>
+      <c r="G90" t="s">
+        <v>50</v>
+      </c>
+      <c r="H90" t="s">
+        <v>36</v>
+      </c>
+      <c r="I90" t="s">
+        <v>16</v>
+      </c>
+      <c r="K90">
+        <v>100</v>
+      </c>
+      <c r="L90">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>20</v>
+      </c>
+      <c r="B91">
+        <v>720</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91" t="s">
+        <v>21</v>
+      </c>
+      <c r="E91" t="s">
+        <v>31</v>
+      </c>
+      <c r="F91" t="s">
+        <v>24</v>
+      </c>
+      <c r="G91" t="s">
+        <v>50</v>
+      </c>
+      <c r="H91" t="s">
+        <v>36</v>
+      </c>
+      <c r="I91" t="s">
+        <v>16</v>
+      </c>
+      <c r="K91">
+        <v>100</v>
+      </c>
+      <c r="L91">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92">
+        <v>16</v>
+      </c>
+      <c r="C92">
+        <v>18</v>
+      </c>
+      <c r="D92" t="s">
+        <v>73</v>
+      </c>
+      <c r="E92" t="s">
+        <v>71</v>
+      </c>
+      <c r="F92" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" t="s">
+        <v>62</v>
+      </c>
+      <c r="H92" t="s">
+        <v>36</v>
+      </c>
+      <c r="I92" t="s">
+        <v>16</v>
+      </c>
+      <c r="K92">
+        <v>100</v>
+      </c>
+      <c r="L92">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93">
+        <v>4</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93" t="s">
+        <v>72</v>
+      </c>
+      <c r="E93" t="s">
+        <v>71</v>
+      </c>
+      <c r="F93" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93" t="s">
+        <v>62</v>
+      </c>
+      <c r="H93" t="s">
+        <v>36</v>
+      </c>
+      <c r="I93" t="s">
+        <v>16</v>
+      </c>
+      <c r="K93">
+        <v>100</v>
+      </c>
+      <c r="L93">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>18</v>
+      </c>
+      <c r="B94">
+        <v>24</v>
+      </c>
+      <c r="C94">
+        <v>24</v>
+      </c>
+      <c r="D94" t="s">
+        <v>33</v>
+      </c>
+      <c r="E94" t="s">
+        <v>71</v>
+      </c>
+      <c r="F94" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" t="s">
+        <v>62</v>
+      </c>
+      <c r="H94" t="s">
+        <v>36</v>
+      </c>
+      <c r="I94" t="s">
+        <v>16</v>
+      </c>
+      <c r="K94">
+        <v>100</v>
+      </c>
+      <c r="L94">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95">
+        <v>57</v>
+      </c>
+      <c r="C95">
+        <v>61</v>
+      </c>
+      <c r="D95" t="s">
+        <v>29</v>
+      </c>
+      <c r="E95" t="s">
+        <v>71</v>
+      </c>
+      <c r="F95" t="s">
+        <v>14</v>
+      </c>
+      <c r="G95" t="s">
+        <v>62</v>
+      </c>
+      <c r="H95" t="s">
+        <v>36</v>
+      </c>
+      <c r="I95" t="s">
+        <v>16</v>
+      </c>
+      <c r="K95">
+        <v>100</v>
+      </c>
+      <c r="L95">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>20</v>
+      </c>
+      <c r="B96">
+        <v>478</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" t="s">
+        <v>71</v>
+      </c>
+      <c r="F96" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96" t="s">
+        <v>62</v>
+      </c>
+      <c r="H96" t="s">
+        <v>36</v>
+      </c>
+      <c r="I96" t="s">
+        <v>16</v>
+      </c>
+      <c r="K96">
+        <v>100</v>
+      </c>
+      <c r="L96">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97">
+        <v>24</v>
+      </c>
+      <c r="C97">
+        <v>16</v>
+      </c>
+      <c r="D97" t="s">
+        <v>30</v>
+      </c>
+      <c r="E97" t="s">
+        <v>68</v>
+      </c>
+      <c r="F97" t="s">
+        <v>23</v>
+      </c>
+      <c r="G97" t="s">
+        <v>62</v>
+      </c>
+      <c r="H97" t="s">
+        <v>36</v>
+      </c>
+      <c r="I97" t="s">
+        <v>16</v>
+      </c>
+      <c r="K97">
+        <v>100</v>
+      </c>
+      <c r="L97">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98">
+        <v>6</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98" t="s">
+        <v>70</v>
+      </c>
+      <c r="E98" t="s">
+        <v>68</v>
+      </c>
+      <c r="F98" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" t="s">
+        <v>62</v>
+      </c>
+      <c r="H98" t="s">
+        <v>36</v>
+      </c>
+      <c r="I98" t="s">
+        <v>16</v>
+      </c>
+      <c r="K98">
+        <v>100</v>
+      </c>
+      <c r="L98">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>18</v>
+      </c>
+      <c r="B99">
+        <v>36</v>
+      </c>
+      <c r="C99">
+        <v>32</v>
+      </c>
+      <c r="D99" t="s">
+        <v>57</v>
+      </c>
+      <c r="E99" t="s">
+        <v>68</v>
+      </c>
+      <c r="F99" t="s">
+        <v>23</v>
+      </c>
+      <c r="G99" t="s">
+        <v>62</v>
+      </c>
+      <c r="H99" t="s">
+        <v>36</v>
+      </c>
+      <c r="I99" t="s">
+        <v>16</v>
+      </c>
+      <c r="K99">
+        <v>100</v>
+      </c>
+      <c r="L99">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>19</v>
+      </c>
+      <c r="B100">
+        <v>86</v>
+      </c>
+      <c r="C100">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" t="s">
+        <v>68</v>
+      </c>
+      <c r="F100" t="s">
+        <v>23</v>
+      </c>
+      <c r="G100" t="s">
+        <v>62</v>
+      </c>
+      <c r="H100" t="s">
+        <v>36</v>
+      </c>
+      <c r="I100" t="s">
+        <v>16</v>
+      </c>
+      <c r="K100">
+        <v>100</v>
+      </c>
+      <c r="L100">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>20</v>
+      </c>
+      <c r="B101">
+        <v>717</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101" t="s">
+        <v>21</v>
+      </c>
+      <c r="E101" t="s">
+        <v>68</v>
+      </c>
+      <c r="F101" t="s">
+        <v>23</v>
+      </c>
+      <c r="G101" t="s">
+        <v>62</v>
+      </c>
+      <c r="H101" t="s">
+        <v>36</v>
+      </c>
+      <c r="I101" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101">
+        <v>100</v>
+      </c>
+      <c r="L101">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102">
+        <v>10</v>
+      </c>
+      <c r="C102">
+        <v>15</v>
+      </c>
+      <c r="D102" t="s">
+        <v>66</v>
+      </c>
+      <c r="E102" t="s">
+        <v>63</v>
+      </c>
+      <c r="F102" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" t="s">
+        <v>62</v>
+      </c>
+      <c r="H102" t="s">
+        <v>36</v>
+      </c>
+      <c r="I102" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" t="s">
+        <v>67</v>
+      </c>
+      <c r="K102">
+        <v>100</v>
+      </c>
+      <c r="L102">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>17</v>
+      </c>
+      <c r="B103">
+        <v>2</v>
+      </c>
+      <c r="C103">
+        <v>3</v>
+      </c>
+      <c r="D103" t="s">
+        <v>66</v>
+      </c>
+      <c r="E103" t="s">
+        <v>63</v>
+      </c>
+      <c r="F103" t="s">
+        <v>23</v>
+      </c>
+      <c r="G103" t="s">
+        <v>62</v>
+      </c>
+      <c r="H103" t="s">
+        <v>36</v>
+      </c>
+      <c r="I103" t="s">
+        <v>16</v>
+      </c>
+      <c r="K103">
+        <v>100</v>
+      </c>
+      <c r="L103">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>18</v>
+      </c>
+      <c r="B104">
+        <v>15</v>
+      </c>
+      <c r="C104">
+        <v>14</v>
+      </c>
+      <c r="D104" t="s">
+        <v>65</v>
+      </c>
+      <c r="E104" t="s">
+        <v>63</v>
+      </c>
+      <c r="F104" t="s">
+        <v>23</v>
+      </c>
+      <c r="G104" t="s">
+        <v>62</v>
+      </c>
+      <c r="H104" t="s">
+        <v>36</v>
+      </c>
+      <c r="I104" t="s">
+        <v>16</v>
+      </c>
+      <c r="K104">
+        <v>100</v>
+      </c>
+      <c r="L104">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>19</v>
+      </c>
+      <c r="B105">
+        <v>37</v>
+      </c>
+      <c r="C105">
+        <v>46</v>
+      </c>
+      <c r="D105" t="s">
+        <v>64</v>
+      </c>
+      <c r="E105" t="s">
+        <v>63</v>
+      </c>
+      <c r="F105" t="s">
+        <v>23</v>
+      </c>
+      <c r="G105" t="s">
+        <v>62</v>
+      </c>
+      <c r="H105" t="s">
+        <v>36</v>
+      </c>
+      <c r="I105" t="s">
+        <v>16</v>
+      </c>
+      <c r="K105">
+        <v>100</v>
+      </c>
+      <c r="L105">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>20</v>
+      </c>
+      <c r="B106">
+        <v>305</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106" t="s">
+        <v>21</v>
+      </c>
+      <c r="E106" t="s">
+        <v>63</v>
+      </c>
+      <c r="F106" t="s">
+        <v>23</v>
+      </c>
+      <c r="G106" t="s">
+        <v>62</v>
+      </c>
+      <c r="H106" t="s">
+        <v>36</v>
+      </c>
+      <c r="I106" t="s">
+        <v>16</v>
+      </c>
+      <c r="K106">
+        <v>100</v>
+      </c>
+      <c r="L106">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/05 Mayo/Liquidacióncvs - VENTAS - CONDICIONAL SABA/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/05 Mayo/Liquidacióncvs - FINAL/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_6B7902D85257D20E62355476585DCE3A87478B38" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40C03C10-59A8-4053-9A80-0118191228DD}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_3ACD539117770C0E62355476585DCE3A874653C5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0371FAC0-B761-4234-A9B9-C68FFAE1C80A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="181">
   <si>
     <t>Producto</t>
   </si>
@@ -61,314 +61,527 @@
     <t>POSTPAGO</t>
   </si>
   <si>
+    <t>90%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>LIDER</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>Sin pago (0%)</t>
+  </si>
+  <si>
+    <t>HOGAR</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>TERMINALES</t>
+  </si>
+  <si>
+    <t>45%</t>
+  </si>
+  <si>
+    <t>OTROS</t>
+  </si>
+  <si>
+    <t>65%</t>
+  </si>
+  <si>
+    <t>CVS PLUS</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>ASESOR</t>
+  </si>
+  <si>
+    <t>157%</t>
+  </si>
+  <si>
+    <t>103%</t>
+  </si>
+  <si>
+    <t>107%</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Posada Galeano</t>
+  </si>
+  <si>
+    <t>Nueva inicia el 15 - mes de gracia hasta el 15 de junio</t>
+  </si>
+  <si>
+    <t>36%</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>111%</t>
+  </si>
+  <si>
+    <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+  </si>
+  <si>
+    <t>COPACABANA</t>
+  </si>
+  <si>
+    <t>120%</t>
+  </si>
+  <si>
+    <t>94%</t>
+  </si>
+  <si>
+    <t>118%</t>
+  </si>
+  <si>
+    <t>Alexandra Patricia Duque</t>
+  </si>
+  <si>
+    <t>171%</t>
+  </si>
+  <si>
+    <t>98%</t>
+  </si>
+  <si>
+    <t>81%</t>
+  </si>
+  <si>
+    <t>138%</t>
+  </si>
+  <si>
+    <t>Bibiana Farley Rios Agudelo</t>
+  </si>
+  <si>
+    <t>Ingresa de vacaciones el 21</t>
+  </si>
+  <si>
+    <t>92%</t>
+  </si>
+  <si>
+    <t>112%</t>
+  </si>
+  <si>
+    <t>Lider Marcela Valencia Tabares</t>
+  </si>
+  <si>
+    <t>ITAGUI</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>67%</t>
+  </si>
+  <si>
+    <t>Dailyn Del Valle Alvarez Rueda</t>
+  </si>
+  <si>
+    <t>89%</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
+    <t>150%</t>
+  </si>
+  <si>
+    <t>Jhon Alejandro Cardona Quintero</t>
+  </si>
+  <si>
+    <t>El 19 pasa a Capacitación como líder para el CVS de la Estrella</t>
+  </si>
+  <si>
+    <t>93%</t>
+  </si>
+  <si>
+    <t>124%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
+  </si>
+  <si>
+    <t>BARBOSA</t>
+  </si>
+  <si>
+    <t>134%</t>
+  </si>
+  <si>
+    <t>109%</t>
+  </si>
+  <si>
+    <t>117%</t>
+  </si>
+  <si>
+    <t>Sene Del Socorro Suarez Torres</t>
+  </si>
+  <si>
+    <t>105%</t>
+  </si>
+  <si>
+    <t>6%</t>
+  </si>
+  <si>
+    <t>Evelis Mary Ojeda Baldovino</t>
+  </si>
+  <si>
+    <t>SUPERNUMERARIO</t>
+  </si>
+  <si>
+    <t>Nueva- ingresa el 23 aplica mes de gracia en el mes de Junio</t>
+  </si>
+  <si>
+    <t>7%</t>
+  </si>
+  <si>
+    <t>Sara Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t>como líder 1 día- meta puntos 40  cump 198%       - meta post  1 cump 0%</t>
+  </si>
+  <si>
+    <t>meta 1  cump 0%</t>
+  </si>
+  <si>
+    <t>5%</t>
+  </si>
+  <si>
+    <t>meta 1  cump 200%</t>
+  </si>
+  <si>
+    <t>2%</t>
+  </si>
+  <si>
+    <t>meta 2 cump 50%</t>
+  </si>
+  <si>
+    <t>55%</t>
+  </si>
+  <si>
     <t>Lider Paola Andrea Clavijo</t>
   </si>
   <si>
-    <t>LIDER</t>
-  </si>
-  <si>
     <t>ENVIGADO</t>
   </si>
   <si>
-    <t>Sin pago (0%)</t>
-  </si>
-  <si>
-    <t>HOGAR</t>
-  </si>
-  <si>
-    <t>TERMINALES</t>
-  </si>
-  <si>
-    <t>OTROS</t>
-  </si>
-  <si>
-    <t>CVS PLUS</t>
-  </si>
-  <si>
-    <t>0%</t>
+    <t>Vac del 02 al 20 - meta puntos  328 cump  106%        - meta post 8  cump 138%</t>
+  </si>
+  <si>
+    <t>Meta hogar 2 cump 100%</t>
+  </si>
+  <si>
+    <t>52%</t>
+  </si>
+  <si>
+    <t>Meta terminales 8 cump 150%</t>
+  </si>
+  <si>
+    <t>38%</t>
+  </si>
+  <si>
+    <t>Meta Otros 18 cump 100%</t>
+  </si>
+  <si>
+    <t>37%</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>Darinela  Chavarria Carvajal</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>115%</t>
+  </si>
+  <si>
+    <t>130%</t>
   </si>
   <si>
     <t>Luz Enith Sanchez Galeano</t>
   </si>
   <si>
-    <t>ASESOR</t>
-  </si>
-  <si>
-    <t>SUPERNUMERARIO</t>
+    <t>88%</t>
+  </si>
+  <si>
+    <t>108%</t>
+  </si>
+  <si>
+    <t>10%</t>
   </si>
   <si>
     <t>Kelly Yuliana Ospina Saldarriaga</t>
   </si>
   <si>
+    <t>Cubre 5 días la líder meta puntos 182 cump 62%    meta post 4 cump 75%</t>
+  </si>
+  <si>
+    <t>meta 1 cump 0% cump 60%</t>
+  </si>
+  <si>
+    <t>9%</t>
+  </si>
+  <si>
+    <t>meta 5 cump 60%</t>
+  </si>
+  <si>
     <t>20%</t>
   </si>
   <si>
-    <t>92%</t>
+    <t>meta 10 cump 140%</t>
   </si>
   <si>
     <t>27%</t>
   </si>
   <si>
-    <t>107%</t>
-  </si>
-  <si>
-    <t>67%</t>
-  </si>
-  <si>
-    <t>Sara Julieth Acevedo Gutierrez</t>
+    <t>Líder 4 días- meta puntos  364.5 cump 142%       meta post  8  cump 100%</t>
+  </si>
+  <si>
+    <t>meta 2 cump 100%</t>
+  </si>
+  <si>
+    <t>meta 10  cump 130%</t>
   </si>
   <si>
     <t>42%</t>
   </si>
   <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>123%</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>2026-05</t>
-  </si>
-  <si>
-    <t>Vac del 02 al 20 - meta puntos  328 cump           - meta post 8  cump</t>
-  </si>
-  <si>
-    <t>Meta hogar 2</t>
-  </si>
-  <si>
-    <t>36%</t>
-  </si>
-  <si>
-    <t>Meta terminales 8</t>
+    <t>meta 20  cump 150%</t>
+  </si>
+  <si>
+    <t>136%</t>
+  </si>
+  <si>
+    <t>Lider Leider  Alexander Calderon</t>
+  </si>
+  <si>
+    <t>JUNIN</t>
+  </si>
+  <si>
+    <t>188%</t>
+  </si>
+  <si>
+    <t>62%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Taborda Ruiz</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>127%</t>
+  </si>
+  <si>
+    <t>Jessica Catherine Gutierrez Garcia</t>
+  </si>
+  <si>
+    <t>95%</t>
+  </si>
+  <si>
+    <t>Sandra Milena Carmona Galeano</t>
+  </si>
+  <si>
+    <t>114%</t>
+  </si>
+  <si>
+    <t>3%</t>
+  </si>
+  <si>
+    <t>líder 1 día- meta  puntos  56.6  cump 43% - post cumpl 100%</t>
+  </si>
+  <si>
+    <t>meta 2  cump 0%</t>
+  </si>
+  <si>
+    <t>meta 4  cump 175%</t>
+  </si>
+  <si>
+    <t>LÃ­der Estrella Milton Hernando Barrera Castro</t>
+  </si>
+  <si>
+    <t>LA ESTRELLA</t>
+  </si>
+  <si>
+    <t>Le finalizaron contrato el 15</t>
   </si>
   <si>
     <t>29%</t>
   </si>
   <si>
-    <t>Meta Otros 18</t>
-  </si>
-  <si>
-    <t>73%</t>
-  </si>
-  <si>
-    <t>Darinela  Chavarria Carvajal</t>
+    <t>Yessica  Restrepo Caicedo</t>
+  </si>
+  <si>
+    <t>Incp 5 días -Meta puntos 712.5  cump 61%     meta post  7 cump 86%</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>Meta  4  cump 75%</t>
+  </si>
+  <si>
+    <t>Meta 14  cump 114%</t>
+  </si>
+  <si>
+    <t>Meta 33  cump 79%</t>
+  </si>
+  <si>
+    <t>8 días líder - meta puntos 200 cump 69% - Meta post 3 cump 200%</t>
+  </si>
+  <si>
+    <t>Meta 2 cump 0%</t>
+  </si>
+  <si>
+    <t>22%</t>
+  </si>
+  <si>
+    <t>Meta 6 cump 67%</t>
+  </si>
+  <si>
+    <t>17%</t>
+  </si>
+  <si>
+    <t>Meta 14 cump 50%</t>
+  </si>
+  <si>
+    <t>LÃ­der Carol Lizet Torres Giraldo</t>
+  </si>
+  <si>
+    <t>ZARAGOZA</t>
+  </si>
+  <si>
+    <t>Cubre caja 4 días - meta puntos 733 cump 85%      meta post  9 cump 100%</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>meta 23  cump 117%</t>
+  </si>
+  <si>
+    <t>106%</t>
+  </si>
+  <si>
+    <t>meta 30  cump 127%</t>
+  </si>
+  <si>
+    <t>Paola Andrea Castillo Perez</t>
   </si>
   <si>
     <t>102%</t>
   </si>
   <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>9%</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>39%</t>
-  </si>
-  <si>
-    <t>LA ESTRELLA</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>22%</t>
-  </si>
-  <si>
-    <t>Yessica  Restrepo Caicedo</t>
-  </si>
-  <si>
-    <t>Meta 33</t>
-  </si>
-  <si>
-    <t>62%</t>
-  </si>
-  <si>
-    <t>Meta 14</t>
-  </si>
-  <si>
-    <t>89%</t>
-  </si>
-  <si>
-    <t>Meta  4</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>LÃ­der Estrella Milton Hernando Barrera Castro</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>ITAGUI</t>
-  </si>
-  <si>
-    <t>Jhon Alejandro Cardona Quintero</t>
-  </si>
-  <si>
-    <t>124%</t>
-  </si>
-  <si>
-    <t>93%</t>
-  </si>
-  <si>
-    <t>150%</t>
-  </si>
-  <si>
-    <t>El 19 pasa a Capacitación como líder para el CVS de la Estrella</t>
-  </si>
-  <si>
-    <t>Dailyn Del Valle Alvarez Rueda</t>
-  </si>
-  <si>
-    <t>79%</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>Lider Marcela Valencia Tabares</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>112%</t>
-  </si>
-  <si>
-    <t>Incp 5 días -Meta puntos 712.5     meta post  7</t>
-  </si>
-  <si>
-    <t>Le finalizaron contrato el 15</t>
-  </si>
-  <si>
-    <t>COPACABANA</t>
-  </si>
-  <si>
-    <t>Bibiana Farley Rios Agudelo</t>
-  </si>
-  <si>
-    <t>Ingresa de vacaciones el 21</t>
-  </si>
-  <si>
-    <t>138%</t>
-  </si>
-  <si>
-    <t>Alexandra Patricia Duque</t>
-  </si>
-  <si>
-    <t>81%</t>
-  </si>
-  <si>
-    <t>98%</t>
-  </si>
-  <si>
-    <t>171%</t>
-  </si>
-  <si>
-    <t>118%</t>
-  </si>
-  <si>
-    <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
-  </si>
-  <si>
-    <t>94%</t>
-  </si>
-  <si>
-    <t>120%</t>
-  </si>
-  <si>
-    <t>111%</t>
-  </si>
-  <si>
-    <t>BARBOSA</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>5%</t>
-  </si>
-  <si>
-    <t>Evelis Mary Ojeda Baldovino</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>Nueva- ingresa el 23 aplica mes de gracia en el mes de Junio</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>Sene Del Socorro Suarez Torres</t>
-  </si>
-  <si>
-    <t>105%</t>
-  </si>
-  <si>
-    <t>83%</t>
-  </si>
-  <si>
-    <t>117%</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
-  </si>
-  <si>
-    <t>145%</t>
-  </si>
-  <si>
-    <t>SABANETA</t>
-  </si>
-  <si>
-    <t>Maria Fernanda Posada Galeano</t>
-  </si>
-  <si>
-    <t>Nueva inicia el 15 - mes de gracia hasta el 15 de junio</t>
-  </si>
-  <si>
-    <t>Andrea  Arenas Hurtado</t>
-  </si>
-  <si>
-    <t>103%</t>
-  </si>
-  <si>
-    <t>157%</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Arbelaez</t>
-  </si>
-  <si>
-    <t>65%</t>
-  </si>
-  <si>
-    <t>45%</t>
-  </si>
-  <si>
-    <t>90%</t>
+    <t>86%</t>
+  </si>
+  <si>
+    <t>Lider Luz Stella Serna</t>
+  </si>
+  <si>
+    <t>TERMINAL NORTE</t>
+  </si>
+  <si>
+    <t>125%</t>
+  </si>
+  <si>
+    <t>139%</t>
+  </si>
+  <si>
+    <t>Cristian Camilo Torres Toro</t>
+  </si>
+  <si>
+    <t>69%</t>
+  </si>
+  <si>
+    <t>Asesora 1 día   meta puntos  66 cump 5%       APOYO</t>
+  </si>
+  <si>
+    <t>meta 1</t>
+  </si>
+  <si>
+    <t>meta 2</t>
+  </si>
+  <si>
+    <t>4%</t>
+  </si>
+  <si>
+    <t>meta 4</t>
+  </si>
+  <si>
+    <t>Lider Girardota Paulina Andrea Zapata Jimenez</t>
+  </si>
+  <si>
+    <t>GIRARDOTA</t>
+  </si>
+  <si>
+    <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+  </si>
+  <si>
+    <t>NUMERARIO</t>
+  </si>
+  <si>
+    <t>Terminal Apoyo 2 días</t>
+  </si>
+  <si>
+    <t>Junín 1 día líder  cump43%</t>
+  </si>
+  <si>
+    <t>Girardota 1 día Apoyo</t>
+  </si>
+  <si>
+    <t>1%</t>
+  </si>
+  <si>
+    <t>Envigado 3 días líder cump 62%</t>
+  </si>
+  <si>
+    <t>Envigado 7 días líder 142%</t>
+  </si>
+  <si>
+    <t>Barbosa 1 día 198%</t>
+  </si>
+  <si>
+    <t>La Estrella 8 días líder 69%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -379,7 +592,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -387,12 +600,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,48 +926,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L176"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44.140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -748,183 +975,171 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="K2">
         <v>100</v>
       </c>
       <c r="L2">
-        <v>27.1</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K3">
         <v>100</v>
       </c>
       <c r="L3">
-        <v>27.1</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>27.1</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B5">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C5">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>27.1</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>375</v>
+        <v>491</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>27.1</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -935,171 +1150,171 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>50.5</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>50.5</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>50.5</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B10">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="C10">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>50.5</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B11">
-        <v>562</v>
+        <v>731</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>50.5</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1107,174 +1322,177 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
         <v>34</v>
       </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" t="s">
-        <v>16</v>
-      </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>94.1</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>94.1</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B14">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C14">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>94.1</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B15">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="C15">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>94.1</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B16">
-        <v>562</v>
+        <v>281</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>94.1</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1282,174 +1500,174 @@
         <v>12</v>
       </c>
       <c r="B17">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H17" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>8.6</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H18" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>8.6</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H19" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>8.6</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B20">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C20">
+        <v>58</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" t="s">
         <v>15</v>
       </c>
-      <c r="D20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" t="s">
-        <v>24</v>
-      </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H20" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>8.6</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B21">
-        <v>562</v>
+        <v>516</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K21">
         <v>100</v>
       </c>
       <c r="L21">
-        <v>8.6</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1457,174 +1675,174 @@
         <v>12</v>
       </c>
       <c r="B22">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>41</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>41</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B24">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C24">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H24" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>41</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B25">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C25">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H25" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>41</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>562</v>
+        <v>774</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H26" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>41</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1632,174 +1850,177 @@
         <v>12</v>
       </c>
       <c r="B27">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C27">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="H27" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J27" t="s">
+        <v>49</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>53.9</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E28" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G28" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="H28" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>53.9</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B29">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G29" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="H29" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>53.9</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B30">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="C30">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="E30" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G30" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="H30" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>53.9</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B31">
-        <v>491</v>
+        <v>211</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G31" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="H31" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>53.9</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -1807,174 +2028,174 @@
         <v>12</v>
       </c>
       <c r="B32">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C32">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H32" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>100.3</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="E33" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H33" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>100.3</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B34">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C34">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="F34" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H34" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34">
-        <v>100.3</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B35">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="C35">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="D35" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E35" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H35" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>100.3</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B36">
-        <v>731</v>
+        <v>478</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H36" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K36">
         <v>100</v>
       </c>
       <c r="L36">
-        <v>100.3</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -1982,177 +2203,174 @@
         <v>12</v>
       </c>
       <c r="B37">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E37" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G37" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H37" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J37" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="K37">
         <v>100</v>
       </c>
       <c r="L37">
-        <v>30.5</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E38" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="F38" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G38" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H38" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K38">
         <v>100</v>
       </c>
       <c r="L38">
-        <v>30.5</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B39">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E39" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G39" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H39" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K39">
         <v>100</v>
       </c>
       <c r="L39">
-        <v>30.5</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B40">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E40" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="F40" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G40" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H40" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K40">
         <v>100</v>
       </c>
       <c r="L40">
-        <v>30.5</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B41">
-        <v>281</v>
+        <v>717</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E41" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G41" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="H41" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K41">
         <v>100</v>
       </c>
       <c r="L41">
-        <v>30.5</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2160,174 +2378,177 @@
         <v>12</v>
       </c>
       <c r="B42">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C42">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G42" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="H42" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J42" t="s">
+        <v>61</v>
       </c>
       <c r="K42">
         <v>100</v>
       </c>
       <c r="L42">
-        <v>96.2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G43" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="H43" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K43">
         <v>100</v>
       </c>
       <c r="L43">
-        <v>96.2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B44">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C44">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E44" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F44" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G44" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="H44" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K44">
         <v>100</v>
       </c>
       <c r="L44">
-        <v>96.2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B45">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C45">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D45" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G45" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="H45" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K45">
         <v>100</v>
       </c>
       <c r="L45">
-        <v>96.2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B46">
-        <v>600</v>
+        <v>305</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G46" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="H46" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K46">
         <v>100</v>
       </c>
       <c r="L46">
-        <v>96.2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2335,174 +2556,174 @@
         <v>12</v>
       </c>
       <c r="B47">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C47">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="E47" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="F47" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H47" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K47">
         <v>100</v>
       </c>
       <c r="L47">
-        <v>107.1</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B48">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H48" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I48" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K48">
         <v>100</v>
       </c>
       <c r="L48">
-        <v>107.1</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B49">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C49">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E49" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="F49" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H49" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K49">
         <v>100</v>
       </c>
       <c r="L49">
-        <v>107.1</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B50">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C50">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="E50" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H50" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I50" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K50">
         <v>100</v>
       </c>
       <c r="L50">
-        <v>107.1</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B51">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>655</v>
       </c>
       <c r="D51" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H51" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K51">
         <v>100</v>
       </c>
       <c r="L51">
-        <v>107.1</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2513,174 +2734,171 @@
         <v>18</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="E52" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F52" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G52" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H52" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I52" t="s">
-        <v>16</v>
-      </c>
-      <c r="J52" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="K52">
         <v>100</v>
       </c>
       <c r="L52">
-        <v>1</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B53">
         <v>6</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E53" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F53" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G53" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H53" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K53">
         <v>100</v>
       </c>
       <c r="L53">
-        <v>1</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B54">
         <v>43</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D54" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E54" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F54" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G54" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H54" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I54" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K54">
         <v>100</v>
       </c>
       <c r="L54">
-        <v>1</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B55">
         <v>57</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="E55" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F55" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G55" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H55" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I55" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K55">
         <v>100</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B56">
         <v>900</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>928</v>
       </c>
       <c r="D56" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F56" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G56" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H56" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I56" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K56">
         <v>100</v>
       </c>
       <c r="L56">
-        <v>1</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -2691,36 +2909,39 @@
         <v>18</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="E57" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F57" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G57" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H57" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J57" t="s">
+        <v>74</v>
       </c>
       <c r="K57">
         <v>100</v>
       </c>
       <c r="L57">
-        <v>5.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B58">
         <v>6</v>
@@ -2729,103 +2950,103 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E58" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F58" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G58" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H58" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I58" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K58">
         <v>100</v>
       </c>
       <c r="L58">
-        <v>5.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B59">
         <v>43</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D59" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="E59" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F59" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G59" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H59" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I59" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K59">
         <v>100</v>
       </c>
       <c r="L59">
-        <v>5.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B60">
         <v>57</v>
       </c>
       <c r="C60">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
+        <v>75</v>
+      </c>
+      <c r="E60" t="s">
+        <v>72</v>
+      </c>
+      <c r="F60" t="s">
+        <v>73</v>
+      </c>
+      <c r="G60" t="s">
+        <v>65</v>
+      </c>
+      <c r="H60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" t="s">
+        <v>18</v>
+      </c>
+      <c r="K60">
+        <v>100</v>
+      </c>
+      <c r="L60">
         <v>1</v>
-      </c>
-      <c r="D60" t="s">
-        <v>90</v>
-      </c>
-      <c r="E60" t="s">
-        <v>31</v>
-      </c>
-      <c r="F60" t="s">
-        <v>24</v>
-      </c>
-      <c r="G60" t="s">
-        <v>89</v>
-      </c>
-      <c r="H60" t="s">
-        <v>36</v>
-      </c>
-      <c r="I60" t="s">
-        <v>16</v>
-      </c>
-      <c r="K60">
-        <v>100</v>
-      </c>
-      <c r="L60">
-        <v>5.5</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B61">
         <v>900</v>
@@ -2834,28 +3055,28 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F61" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G61" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="H61" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I61" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K61">
         <v>100</v>
       </c>
       <c r="L61">
-        <v>5.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -2863,174 +3084,186 @@
         <v>12</v>
       </c>
       <c r="B62">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C62">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D62" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F62" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="G62" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H62" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I62" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J62" t="s">
+        <v>77</v>
       </c>
       <c r="K62">
         <v>100</v>
       </c>
       <c r="L62">
-        <v>114.9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C63">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="E63" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F63" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="G63" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H63" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I63" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J63" t="s">
+        <v>78</v>
       </c>
       <c r="K63">
         <v>100</v>
       </c>
       <c r="L63">
-        <v>114.9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B64">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C64">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D64" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="E64" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F64" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="G64" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H64" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I64" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J64" t="s">
+        <v>80</v>
       </c>
       <c r="K64">
         <v>100</v>
       </c>
       <c r="L64">
-        <v>114.9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B65">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C65">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E65" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F65" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="G65" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H65" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I65" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J65" t="s">
+        <v>82</v>
       </c>
       <c r="K65">
         <v>100</v>
       </c>
       <c r="L65">
-        <v>114.9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B66">
-        <v>516</v>
+        <v>900</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E66" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F66" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="G66" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H66" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I66" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K66">
         <v>100</v>
       </c>
       <c r="L66">
-        <v>114.9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3038,174 +3271,186 @@
         <v>12</v>
       </c>
       <c r="B67">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C67">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D67" t="s">
+        <v>83</v>
+      </c>
+      <c r="E67" t="s">
         <v>84</v>
       </c>
-      <c r="E67" t="s">
-        <v>80</v>
-      </c>
       <c r="F67" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H67" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I67" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J67" t="s">
+        <v>86</v>
       </c>
       <c r="K67">
         <v>100</v>
       </c>
       <c r="L67">
-        <v>110.2</v>
+        <v>39.700000000000003</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B68">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C68">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D68" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F68" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H68" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I68" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J68" t="s">
+        <v>87</v>
       </c>
       <c r="K68">
         <v>100</v>
       </c>
       <c r="L68">
-        <v>110.2</v>
+        <v>39.700000000000003</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B69">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C69">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E69" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F69" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H69" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I69" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J69" t="s">
+        <v>89</v>
       </c>
       <c r="K69">
         <v>100</v>
       </c>
       <c r="L69">
-        <v>110.2</v>
+        <v>39.700000000000003</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B70">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="C70">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="E70" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F70" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H70" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I70" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J70" t="s">
+        <v>91</v>
       </c>
       <c r="K70">
         <v>100</v>
       </c>
       <c r="L70">
-        <v>110.2</v>
+        <v>39.700000000000003</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B71">
-        <v>774</v>
+        <v>375</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="D71" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="E71" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F71" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H71" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I71" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K71">
         <v>100</v>
       </c>
       <c r="L71">
-        <v>110.2</v>
+        <v>39.700000000000003</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3213,177 +3458,174 @@
         <v>12</v>
       </c>
       <c r="B72">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C72">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D72" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="E72" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F72" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G72" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H72" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I72" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" t="s">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="K72">
         <v>100</v>
       </c>
       <c r="L72">
-        <v>115.3</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="E73" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F73" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G73" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H73" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I73" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K73">
         <v>100</v>
       </c>
       <c r="L73">
-        <v>115.3</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B74">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C74">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="E74" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F74" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G74" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H74" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I74" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K74">
         <v>100</v>
       </c>
       <c r="L74">
-        <v>115.3</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B75">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="C75">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D75" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="E75" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F75" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G75" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H75" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I75" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K75">
         <v>100</v>
       </c>
       <c r="L75">
-        <v>115.3</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B76">
-        <v>211</v>
+        <v>563</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="D76" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E76" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F76" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G76" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H76" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I76" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K76">
         <v>100</v>
       </c>
       <c r="L76">
-        <v>115.3</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3391,177 +3633,174 @@
         <v>12</v>
       </c>
       <c r="B77">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D77" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="E77" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="F77" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G77" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H77" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>16</v>
-      </c>
-      <c r="J77" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="K77">
         <v>100</v>
       </c>
       <c r="L77">
-        <v>27.1</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B78">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D78" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="E78" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="F78" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G78" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H78" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I78" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K78">
         <v>100</v>
       </c>
       <c r="L78">
-        <v>27.1</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B79">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="D79" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E79" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="F79" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G79" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H79" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I79" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K79">
         <v>100</v>
       </c>
       <c r="L79">
-        <v>27.1</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B80">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C80">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="D80" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="E80" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="F80" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G80" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H80" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K80">
         <v>100</v>
       </c>
       <c r="L80">
-        <v>27.1</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B81">
-        <v>480</v>
+        <v>563</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="D81" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="F81" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G81" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H81" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I81" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K81">
         <v>100</v>
       </c>
       <c r="L81">
-        <v>27.1</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -3569,186 +3808,186 @@
         <v>12</v>
       </c>
       <c r="B82">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C82">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E82" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F82" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G82" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H82" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I82" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J82" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="K82">
         <v>100</v>
       </c>
       <c r="L82">
-        <v>50.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B83">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="E83" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F83" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G83" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H83" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I83" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J83" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="K83">
         <v>100</v>
       </c>
       <c r="L83">
-        <v>50.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B84">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C84">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="E84" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F84" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G84" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H84" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J84" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="K84">
         <v>100</v>
       </c>
       <c r="L84">
-        <v>50.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B85">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C85">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="E85" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F85" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G85" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H85" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I85" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J85" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K85">
         <v>100</v>
       </c>
       <c r="L85">
-        <v>50.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B86">
-        <v>720</v>
+        <v>563</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E86" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F86" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G86" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H86" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I86" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K86">
         <v>100</v>
       </c>
       <c r="L86">
-        <v>50.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -3756,174 +3995,186 @@
         <v>12</v>
       </c>
       <c r="B87">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C87">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D87" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="E87" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="F87" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G87" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H87" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I87" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J87" t="s">
+        <v>111</v>
       </c>
       <c r="K87">
         <v>100</v>
       </c>
       <c r="L87">
-        <v>15.2</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E88" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="F88" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G88" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H88" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J88" t="s">
+        <v>112</v>
       </c>
       <c r="K88">
         <v>100</v>
       </c>
       <c r="L88">
-        <v>15.2</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B89">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C89">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="E89" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="F89" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G89" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H89" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J89" t="s">
+        <v>113</v>
       </c>
       <c r="K89">
         <v>100</v>
       </c>
       <c r="L89">
-        <v>15.2</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B90">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D90" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="E90" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="F90" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G90" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H90" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I90" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="J90" t="s">
+        <v>115</v>
       </c>
       <c r="K90">
         <v>100</v>
       </c>
       <c r="L90">
-        <v>15.2</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B91">
-        <v>720</v>
+        <v>563</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="F91" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G91" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H91" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I91" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K91">
         <v>100</v>
       </c>
       <c r="L91">
-        <v>15.2</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -3931,174 +4182,174 @@
         <v>12</v>
       </c>
       <c r="B92">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C92">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D92" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="E92" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="F92" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H92" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I92" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K92">
         <v>100</v>
       </c>
       <c r="L92">
-        <v>105.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E93" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="F93" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H93" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I93" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K93">
         <v>100</v>
       </c>
       <c r="L93">
-        <v>105.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B94">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C94">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D94" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E94" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="F94" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H94" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K94">
         <v>100</v>
       </c>
       <c r="L94">
-        <v>105.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B95">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="C95">
-        <v>61</v>
+        <v>169</v>
       </c>
       <c r="D95" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="E95" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="F95" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H95" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I95" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K95">
         <v>100</v>
       </c>
       <c r="L95">
-        <v>105.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B96">
-        <v>478</v>
+        <v>300</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D96" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="E96" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="F96" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H96" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I96" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K96">
         <v>100</v>
       </c>
       <c r="L96">
-        <v>105.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4106,174 +4357,174 @@
         <v>12</v>
       </c>
       <c r="B97">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C97">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="D97" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E97" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="F97" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G97" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H97" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I97" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K97">
         <v>100</v>
       </c>
       <c r="L97">
-        <v>75.599999999999994</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B98">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="E98" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="F98" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G98" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H98" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I98" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K98">
         <v>100</v>
       </c>
       <c r="L98">
-        <v>75.599999999999994</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B99">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C99">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D99" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E99" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="F99" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G99" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H99" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I99" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K99">
         <v>100</v>
       </c>
       <c r="L99">
-        <v>75.599999999999994</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B100">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="C100">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="D100" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E100" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="F100" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G100" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H100" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I100" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K100">
         <v>100</v>
       </c>
       <c r="L100">
-        <v>75.599999999999994</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B101">
-        <v>717</v>
+        <v>399</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="D101" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="E101" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="F101" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G101" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H101" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I101" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K101">
         <v>100</v>
       </c>
       <c r="L101">
-        <v>75.599999999999994</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4281,177 +4532,2705 @@
         <v>12</v>
       </c>
       <c r="B102">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C102">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="D102" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="E102" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F102" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G102" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H102" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I102" t="s">
-        <v>16</v>
-      </c>
-      <c r="J102" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="K102">
         <v>100</v>
       </c>
       <c r="L102">
-        <v>116</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C103">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D103" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="E103" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F103" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G103" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H103" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I103" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K103">
         <v>100</v>
       </c>
       <c r="L103">
-        <v>116</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B104">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="C104">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D104" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E104" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F104" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G104" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H104" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I104" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K104">
         <v>100</v>
       </c>
       <c r="L104">
-        <v>116</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B105">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="C105">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="E105" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F105" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G105" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="H105" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I105" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K105">
         <v>100</v>
       </c>
       <c r="L105">
-        <v>116</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106">
+        <v>399</v>
+      </c>
+      <c r="C106">
+        <v>186</v>
+      </c>
+      <c r="D106" t="s">
+        <v>96</v>
+      </c>
+      <c r="E106" t="s">
+        <v>124</v>
+      </c>
+      <c r="F106" t="s">
+        <v>29</v>
+      </c>
+      <c r="G106" t="s">
+        <v>118</v>
+      </c>
+      <c r="H106" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106" t="s">
+        <v>18</v>
+      </c>
+      <c r="K106">
+        <v>100</v>
+      </c>
+      <c r="L106">
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107">
+        <v>37</v>
+      </c>
+      <c r="C107">
+        <v>39</v>
+      </c>
+      <c r="D107" t="s">
+        <v>70</v>
+      </c>
+      <c r="E107" t="s">
+        <v>126</v>
+      </c>
+      <c r="F107" t="s">
+        <v>29</v>
+      </c>
+      <c r="G107" t="s">
+        <v>118</v>
+      </c>
+      <c r="H107" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" t="s">
+        <v>18</v>
+      </c>
+      <c r="K107">
+        <v>100</v>
+      </c>
+      <c r="L107">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>19</v>
+      </c>
+      <c r="B108">
+        <v>4</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="D108" t="s">
+        <v>26</v>
+      </c>
+      <c r="E108" t="s">
+        <v>126</v>
+      </c>
+      <c r="F108" t="s">
+        <v>29</v>
+      </c>
+      <c r="G108" t="s">
+        <v>118</v>
+      </c>
+      <c r="H108" t="s">
+        <v>17</v>
+      </c>
+      <c r="I108" t="s">
+        <v>18</v>
+      </c>
+      <c r="K108">
+        <v>100</v>
+      </c>
+      <c r="L108">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>21</v>
+      </c>
+      <c r="B109">
+        <v>59</v>
+      </c>
+      <c r="C109">
+        <v>67</v>
+      </c>
+      <c r="D109" t="s">
+        <v>127</v>
+      </c>
+      <c r="E109" t="s">
+        <v>126</v>
+      </c>
+      <c r="F109" t="s">
+        <v>29</v>
+      </c>
+      <c r="G109" t="s">
+        <v>118</v>
+      </c>
+      <c r="H109" t="s">
+        <v>17</v>
+      </c>
+      <c r="I109" t="s">
+        <v>18</v>
+      </c>
+      <c r="K109">
+        <v>100</v>
+      </c>
+      <c r="L109">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>23</v>
+      </c>
+      <c r="B110">
+        <v>120</v>
+      </c>
+      <c r="C110">
+        <v>90</v>
+      </c>
+      <c r="D110" t="s">
+        <v>122</v>
+      </c>
+      <c r="E110" t="s">
+        <v>126</v>
+      </c>
+      <c r="F110" t="s">
+        <v>29</v>
+      </c>
+      <c r="G110" t="s">
+        <v>118</v>
+      </c>
+      <c r="H110" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110" t="s">
+        <v>18</v>
+      </c>
+      <c r="K110">
+        <v>100</v>
+      </c>
+      <c r="L110">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>25</v>
+      </c>
+      <c r="B111">
+        <v>399</v>
+      </c>
+      <c r="C111">
+        <v>186</v>
+      </c>
+      <c r="D111" t="s">
+        <v>96</v>
+      </c>
+      <c r="E111" t="s">
+        <v>126</v>
+      </c>
+      <c r="F111" t="s">
+        <v>29</v>
+      </c>
+      <c r="G111" t="s">
+        <v>118</v>
+      </c>
+      <c r="H111" t="s">
+        <v>17</v>
+      </c>
+      <c r="I111" t="s">
+        <v>18</v>
+      </c>
+      <c r="K111">
+        <v>100</v>
+      </c>
+      <c r="L111">
+        <v>91.7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>12</v>
+      </c>
+      <c r="B112">
+        <v>37</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112" t="s">
+        <v>128</v>
+      </c>
+      <c r="E112" t="s">
+        <v>103</v>
+      </c>
+      <c r="F112" t="s">
+        <v>73</v>
+      </c>
+      <c r="G112" t="s">
+        <v>118</v>
+      </c>
+      <c r="H112" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" t="s">
+        <v>129</v>
+      </c>
+      <c r="K112">
+        <v>100</v>
+      </c>
+      <c r="L112">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>19</v>
+      </c>
+      <c r="B113">
+        <v>4</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113" t="s">
+        <v>26</v>
+      </c>
+      <c r="E113" t="s">
+        <v>103</v>
+      </c>
+      <c r="F113" t="s">
+        <v>73</v>
+      </c>
+      <c r="G113" t="s">
+        <v>118</v>
+      </c>
+      <c r="H113" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113" t="s">
+        <v>18</v>
+      </c>
+      <c r="J113" t="s">
+        <v>78</v>
+      </c>
+      <c r="K113">
+        <v>100</v>
+      </c>
+      <c r="L113">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>21</v>
+      </c>
+      <c r="B114">
+        <v>59</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114" t="s">
+        <v>26</v>
+      </c>
+      <c r="E114" t="s">
+        <v>103</v>
+      </c>
+      <c r="F114" t="s">
+        <v>73</v>
+      </c>
+      <c r="G114" t="s">
+        <v>118</v>
+      </c>
+      <c r="H114" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114" t="s">
+        <v>18</v>
+      </c>
+      <c r="J114" t="s">
+        <v>130</v>
+      </c>
+      <c r="K114">
+        <v>100</v>
+      </c>
+      <c r="L114">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>23</v>
+      </c>
+      <c r="B115">
+        <v>120</v>
+      </c>
+      <c r="C115">
+        <v>7</v>
+      </c>
+      <c r="D115" t="s">
+        <v>71</v>
+      </c>
+      <c r="E115" t="s">
+        <v>103</v>
+      </c>
+      <c r="F115" t="s">
+        <v>73</v>
+      </c>
+      <c r="G115" t="s">
+        <v>118</v>
+      </c>
+      <c r="H115" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" t="s">
+        <v>131</v>
+      </c>
+      <c r="K115">
+        <v>100</v>
+      </c>
+      <c r="L115">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>25</v>
+      </c>
+      <c r="B116">
+        <v>399</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116" t="s">
+        <v>26</v>
+      </c>
+      <c r="E116" t="s">
+        <v>103</v>
+      </c>
+      <c r="F116" t="s">
+        <v>73</v>
+      </c>
+      <c r="G116" t="s">
+        <v>118</v>
+      </c>
+      <c r="H116" t="s">
+        <v>17</v>
+      </c>
+      <c r="I116" t="s">
+        <v>18</v>
+      </c>
+      <c r="K116">
+        <v>100</v>
+      </c>
+      <c r="L116">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>12</v>
+      </c>
+      <c r="B117">
+        <v>6</v>
+      </c>
+      <c r="C117">
+        <v>3</v>
+      </c>
+      <c r="D117" t="s">
+        <v>95</v>
+      </c>
+      <c r="E117" t="s">
+        <v>132</v>
+      </c>
+      <c r="F117" t="s">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s">
+        <v>133</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" t="s">
+        <v>134</v>
+      </c>
+      <c r="K117">
+        <v>100</v>
+      </c>
+      <c r="L117">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118">
+        <v>3</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118" t="s">
+        <v>26</v>
+      </c>
+      <c r="E118" t="s">
+        <v>132</v>
+      </c>
+      <c r="F118" t="s">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s">
+        <v>133</v>
+      </c>
+      <c r="H118" t="s">
+        <v>17</v>
+      </c>
+      <c r="I118" t="s">
+        <v>18</v>
+      </c>
+      <c r="K118">
+        <v>100</v>
+      </c>
+      <c r="L118">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>21</v>
+      </c>
+      <c r="B119">
+        <v>12</v>
+      </c>
+      <c r="C119">
+        <v>5</v>
+      </c>
+      <c r="D119" t="s">
+        <v>114</v>
+      </c>
+      <c r="E119" t="s">
+        <v>132</v>
+      </c>
+      <c r="F119" t="s">
+        <v>15</v>
+      </c>
+      <c r="G119" t="s">
+        <v>133</v>
+      </c>
+      <c r="H119" t="s">
+        <v>17</v>
+      </c>
+      <c r="I119" t="s">
+        <v>18</v>
+      </c>
+      <c r="K119">
+        <v>100</v>
+      </c>
+      <c r="L119">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>23</v>
+      </c>
+      <c r="B120">
+        <v>28</v>
+      </c>
+      <c r="C120">
+        <v>8</v>
+      </c>
+      <c r="D120" t="s">
+        <v>135</v>
+      </c>
+      <c r="E120" t="s">
+        <v>132</v>
+      </c>
+      <c r="F120" t="s">
+        <v>15</v>
+      </c>
+      <c r="G120" t="s">
+        <v>133</v>
+      </c>
+      <c r="H120" t="s">
+        <v>17</v>
+      </c>
+      <c r="I120" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120">
+        <v>100</v>
+      </c>
+      <c r="L120">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>25</v>
+      </c>
+      <c r="B121">
+        <v>480</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121" t="s">
+        <v>26</v>
+      </c>
+      <c r="E121" t="s">
+        <v>132</v>
+      </c>
+      <c r="F121" t="s">
+        <v>15</v>
+      </c>
+      <c r="G121" t="s">
+        <v>133</v>
+      </c>
+      <c r="H121" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121" t="s">
+        <v>18</v>
+      </c>
+      <c r="K121">
+        <v>100</v>
+      </c>
+      <c r="L121">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>12</v>
+      </c>
+      <c r="B122">
+        <v>9</v>
+      </c>
+      <c r="C122">
+        <v>6</v>
+      </c>
+      <c r="D122" t="s">
+        <v>55</v>
+      </c>
+      <c r="E122" t="s">
+        <v>136</v>
+      </c>
+      <c r="F122" t="s">
+        <v>29</v>
+      </c>
+      <c r="G122" t="s">
+        <v>133</v>
+      </c>
+      <c r="H122" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" t="s">
+        <v>137</v>
+      </c>
+      <c r="K122">
+        <v>100</v>
+      </c>
+      <c r="L122">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>19</v>
+      </c>
+      <c r="B123">
+        <v>5</v>
+      </c>
+      <c r="C123">
+        <v>3</v>
+      </c>
+      <c r="D123" t="s">
+        <v>138</v>
+      </c>
+      <c r="E123" t="s">
+        <v>136</v>
+      </c>
+      <c r="F123" t="s">
+        <v>29</v>
+      </c>
+      <c r="G123" t="s">
+        <v>133</v>
+      </c>
+      <c r="H123" t="s">
+        <v>17</v>
+      </c>
+      <c r="I123" t="s">
+        <v>18</v>
+      </c>
+      <c r="J123" t="s">
+        <v>139</v>
+      </c>
+      <c r="K123">
+        <v>100</v>
+      </c>
+      <c r="L123">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>21</v>
+      </c>
+      <c r="B124">
+        <v>18</v>
+      </c>
+      <c r="C124">
+        <v>16</v>
+      </c>
+      <c r="D124" t="s">
+        <v>57</v>
+      </c>
+      <c r="E124" t="s">
+        <v>136</v>
+      </c>
+      <c r="F124" t="s">
+        <v>29</v>
+      </c>
+      <c r="G124" t="s">
+        <v>133</v>
+      </c>
+      <c r="H124" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124" t="s">
+        <v>18</v>
+      </c>
+      <c r="J124" t="s">
+        <v>140</v>
+      </c>
+      <c r="K124">
+        <v>100</v>
+      </c>
+      <c r="L124">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>23</v>
+      </c>
+      <c r="B125">
+        <v>42</v>
+      </c>
+      <c r="C125">
+        <v>26</v>
+      </c>
+      <c r="D125" t="s">
+        <v>120</v>
+      </c>
+      <c r="E125" t="s">
+        <v>136</v>
+      </c>
+      <c r="F125" t="s">
+        <v>29</v>
+      </c>
+      <c r="G125" t="s">
+        <v>133</v>
+      </c>
+      <c r="H125" t="s">
+        <v>17</v>
+      </c>
+      <c r="I125" t="s">
+        <v>18</v>
+      </c>
+      <c r="J125" t="s">
+        <v>141</v>
+      </c>
+      <c r="K125">
+        <v>100</v>
+      </c>
+      <c r="L125">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>25</v>
+      </c>
+      <c r="B126">
+        <v>720</v>
+      </c>
+      <c r="C126">
+        <v>721</v>
+      </c>
+      <c r="D126" t="s">
+        <v>27</v>
+      </c>
+      <c r="E126" t="s">
+        <v>136</v>
+      </c>
+      <c r="F126" t="s">
+        <v>29</v>
+      </c>
+      <c r="G126" t="s">
+        <v>133</v>
+      </c>
+      <c r="H126" t="s">
+        <v>17</v>
+      </c>
+      <c r="I126" t="s">
+        <v>18</v>
+      </c>
+      <c r="K126">
+        <v>100</v>
+      </c>
+      <c r="L126">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>12</v>
+      </c>
+      <c r="B127">
+        <v>9</v>
+      </c>
+      <c r="C127">
+        <v>6</v>
+      </c>
+      <c r="D127" t="s">
+        <v>55</v>
+      </c>
+      <c r="E127" t="s">
+        <v>76</v>
+      </c>
+      <c r="F127" t="s">
+        <v>73</v>
+      </c>
+      <c r="G127" t="s">
+        <v>133</v>
+      </c>
+      <c r="H127" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" t="s">
+        <v>142</v>
+      </c>
+      <c r="K127">
+        <v>100</v>
+      </c>
+      <c r="L127">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>19</v>
+      </c>
+      <c r="B128">
+        <v>5</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128" t="s">
+        <v>26</v>
+      </c>
+      <c r="E128" t="s">
+        <v>76</v>
+      </c>
+      <c r="F128" t="s">
+        <v>73</v>
+      </c>
+      <c r="G128" t="s">
+        <v>133</v>
+      </c>
+      <c r="H128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" t="s">
+        <v>143</v>
+      </c>
+      <c r="K128">
+        <v>100</v>
+      </c>
+      <c r="L128">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>21</v>
+      </c>
+      <c r="B129">
+        <v>18</v>
+      </c>
+      <c r="C129">
+        <v>4</v>
+      </c>
+      <c r="D129" t="s">
+        <v>144</v>
+      </c>
+      <c r="E129" t="s">
+        <v>76</v>
+      </c>
+      <c r="F129" t="s">
+        <v>73</v>
+      </c>
+      <c r="G129" t="s">
+        <v>133</v>
+      </c>
+      <c r="H129" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" t="s">
+        <v>145</v>
+      </c>
+      <c r="K129">
+        <v>100</v>
+      </c>
+      <c r="L129">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>23</v>
+      </c>
+      <c r="B130">
+        <v>42</v>
+      </c>
+      <c r="C130">
+        <v>7</v>
+      </c>
+      <c r="D130" t="s">
+        <v>146</v>
+      </c>
+      <c r="E130" t="s">
+        <v>76</v>
+      </c>
+      <c r="F130" t="s">
+        <v>73</v>
+      </c>
+      <c r="G130" t="s">
+        <v>133</v>
+      </c>
+      <c r="H130" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130" t="s">
+        <v>18</v>
+      </c>
+      <c r="J130" t="s">
+        <v>147</v>
+      </c>
+      <c r="K130">
+        <v>100</v>
+      </c>
+      <c r="L130">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+      <c r="B131">
+        <v>720</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131" t="s">
+        <v>26</v>
+      </c>
+      <c r="E131" t="s">
+        <v>76</v>
+      </c>
+      <c r="F131" t="s">
+        <v>73</v>
+      </c>
+      <c r="G131" t="s">
+        <v>133</v>
+      </c>
+      <c r="H131" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131" t="s">
+        <v>18</v>
+      </c>
+      <c r="K131">
+        <v>100</v>
+      </c>
+      <c r="L131">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>12</v>
+      </c>
+      <c r="B132">
+        <v>10</v>
+      </c>
+      <c r="C132">
+        <v>9</v>
+      </c>
+      <c r="D132" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" t="s">
+        <v>148</v>
+      </c>
+      <c r="F132" t="s">
+        <v>15</v>
+      </c>
+      <c r="G132" t="s">
+        <v>149</v>
+      </c>
+      <c r="H132" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" t="s">
+        <v>150</v>
+      </c>
+      <c r="K132">
+        <v>100</v>
+      </c>
+      <c r="L132">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>19</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133" t="s">
+        <v>26</v>
+      </c>
+      <c r="E133" t="s">
+        <v>148</v>
+      </c>
+      <c r="F133" t="s">
+        <v>15</v>
+      </c>
+      <c r="G133" t="s">
+        <v>149</v>
+      </c>
+      <c r="H133" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" t="s">
+        <v>18</v>
+      </c>
+      <c r="K133">
+        <v>100</v>
+      </c>
+      <c r="L133">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>21</v>
+      </c>
+      <c r="B134">
+        <v>28</v>
+      </c>
+      <c r="C134">
+        <v>27</v>
+      </c>
+      <c r="D134" t="s">
+        <v>151</v>
+      </c>
+      <c r="E134" t="s">
+        <v>148</v>
+      </c>
+      <c r="F134" t="s">
+        <v>15</v>
+      </c>
+      <c r="G134" t="s">
+        <v>149</v>
+      </c>
+      <c r="H134" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" t="s">
+        <v>152</v>
+      </c>
+      <c r="K134">
+        <v>100</v>
+      </c>
+      <c r="L134">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>23</v>
+      </c>
+      <c r="B135">
+        <v>36</v>
+      </c>
+      <c r="C135">
+        <v>38</v>
+      </c>
+      <c r="D135" t="s">
+        <v>153</v>
+      </c>
+      <c r="E135" t="s">
+        <v>148</v>
+      </c>
+      <c r="F135" t="s">
+        <v>15</v>
+      </c>
+      <c r="G135" t="s">
+        <v>149</v>
+      </c>
+      <c r="H135" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" t="s">
+        <v>18</v>
+      </c>
+      <c r="J135" t="s">
+        <v>154</v>
+      </c>
+      <c r="K135">
+        <v>100</v>
+      </c>
+      <c r="L135">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>25</v>
+      </c>
+      <c r="B136">
+        <v>480</v>
+      </c>
+      <c r="C136">
+        <v>562</v>
+      </c>
+      <c r="D136" t="s">
+        <v>68</v>
+      </c>
+      <c r="E136" t="s">
+        <v>148</v>
+      </c>
+      <c r="F136" t="s">
+        <v>15</v>
+      </c>
+      <c r="G136" t="s">
+        <v>149</v>
+      </c>
+      <c r="H136" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" t="s">
+        <v>18</v>
+      </c>
+      <c r="K136">
+        <v>100</v>
+      </c>
+      <c r="L136">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137">
+        <v>14</v>
+      </c>
+      <c r="C137">
+        <v>14</v>
+      </c>
+      <c r="D137" t="s">
+        <v>27</v>
+      </c>
+      <c r="E137" t="s">
+        <v>155</v>
+      </c>
+      <c r="F137" t="s">
+        <v>29</v>
+      </c>
+      <c r="G137" t="s">
+        <v>149</v>
+      </c>
+      <c r="H137" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137" t="s">
+        <v>18</v>
+      </c>
+      <c r="K137">
+        <v>100</v>
+      </c>
+      <c r="L137">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>19</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138" t="s">
+        <v>26</v>
+      </c>
+      <c r="E138" t="s">
+        <v>155</v>
+      </c>
+      <c r="F138" t="s">
+        <v>29</v>
+      </c>
+      <c r="G138" t="s">
+        <v>149</v>
+      </c>
+      <c r="H138" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" t="s">
+        <v>18</v>
+      </c>
+      <c r="K138">
+        <v>100</v>
+      </c>
+      <c r="L138">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>21</v>
+      </c>
+      <c r="B139">
+        <v>42</v>
+      </c>
+      <c r="C139">
+        <v>43</v>
+      </c>
+      <c r="D139" t="s">
+        <v>156</v>
+      </c>
+      <c r="E139" t="s">
+        <v>155</v>
+      </c>
+      <c r="F139" t="s">
+        <v>29</v>
+      </c>
+      <c r="G139" t="s">
+        <v>149</v>
+      </c>
+      <c r="H139" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139" t="s">
+        <v>18</v>
+      </c>
+      <c r="K139">
+        <v>100</v>
+      </c>
+      <c r="L139">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>23</v>
+      </c>
+      <c r="B140">
+        <v>54</v>
+      </c>
+      <c r="C140">
+        <v>55</v>
+      </c>
+      <c r="D140" t="s">
+        <v>156</v>
+      </c>
+      <c r="E140" t="s">
+        <v>155</v>
+      </c>
+      <c r="F140" t="s">
+        <v>29</v>
+      </c>
+      <c r="G140" t="s">
+        <v>149</v>
+      </c>
+      <c r="H140" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140" t="s">
+        <v>18</v>
+      </c>
+      <c r="K140">
+        <v>100</v>
+      </c>
+      <c r="L140">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>25</v>
+      </c>
+      <c r="B141">
+        <v>720</v>
+      </c>
+      <c r="C141">
+        <v>809</v>
+      </c>
+      <c r="D141" t="s">
+        <v>51</v>
+      </c>
+      <c r="E141" t="s">
+        <v>155</v>
+      </c>
+      <c r="F141" t="s">
+        <v>29</v>
+      </c>
+      <c r="G141" t="s">
+        <v>149</v>
+      </c>
+      <c r="H141" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" t="s">
+        <v>18</v>
+      </c>
+      <c r="K141">
+        <v>100</v>
+      </c>
+      <c r="L141">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>12</v>
+      </c>
+      <c r="B142">
+        <v>14</v>
+      </c>
+      <c r="C142">
+        <v>12</v>
+      </c>
+      <c r="D142" t="s">
+        <v>157</v>
+      </c>
+      <c r="E142" t="s">
+        <v>158</v>
+      </c>
+      <c r="F142" t="s">
+        <v>15</v>
+      </c>
+      <c r="G142" t="s">
+        <v>159</v>
+      </c>
+      <c r="H142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142" t="s">
+        <v>18</v>
+      </c>
+      <c r="K142">
+        <v>100</v>
+      </c>
+      <c r="L142">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>19</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143" t="s">
+        <v>95</v>
+      </c>
+      <c r="E143" t="s">
+        <v>158</v>
+      </c>
+      <c r="F143" t="s">
+        <v>15</v>
+      </c>
+      <c r="G143" t="s">
+        <v>159</v>
+      </c>
+      <c r="H143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143" t="s">
+        <v>18</v>
+      </c>
+      <c r="K143">
+        <v>100</v>
+      </c>
+      <c r="L143">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>21</v>
+      </c>
+      <c r="B144">
+        <v>28</v>
+      </c>
+      <c r="C144">
+        <v>35</v>
+      </c>
+      <c r="D144" t="s">
+        <v>160</v>
+      </c>
+      <c r="E144" t="s">
+        <v>158</v>
+      </c>
+      <c r="F144" t="s">
+        <v>15</v>
+      </c>
+      <c r="G144" t="s">
+        <v>159</v>
+      </c>
+      <c r="H144" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144" t="s">
+        <v>18</v>
+      </c>
+      <c r="K144">
+        <v>100</v>
+      </c>
+      <c r="L144">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>23</v>
+      </c>
+      <c r="B145">
+        <v>56</v>
+      </c>
+      <c r="C145">
+        <v>78</v>
+      </c>
+      <c r="D145" t="s">
+        <v>161</v>
+      </c>
+      <c r="E145" t="s">
+        <v>158</v>
+      </c>
+      <c r="F145" t="s">
+        <v>15</v>
+      </c>
+      <c r="G145" t="s">
+        <v>159</v>
+      </c>
+      <c r="H145" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145" t="s">
+        <v>18</v>
+      </c>
+      <c r="K145">
+        <v>100</v>
+      </c>
+      <c r="L145">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>25</v>
+      </c>
+      <c r="B146">
+        <v>600</v>
+      </c>
+      <c r="C146">
+        <v>750</v>
+      </c>
+      <c r="D146" t="s">
+        <v>160</v>
+      </c>
+      <c r="E146" t="s">
+        <v>158</v>
+      </c>
+      <c r="F146" t="s">
+        <v>15</v>
+      </c>
+      <c r="G146" t="s">
+        <v>159</v>
+      </c>
+      <c r="H146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146" t="s">
+        <v>18</v>
+      </c>
+      <c r="K146">
+        <v>100</v>
+      </c>
+      <c r="L146">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>12</v>
+      </c>
+      <c r="B147">
+        <v>21</v>
+      </c>
+      <c r="C147">
+        <v>18</v>
+      </c>
+      <c r="D147" t="s">
+        <v>157</v>
+      </c>
+      <c r="E147" t="s">
+        <v>162</v>
+      </c>
+      <c r="F147" t="s">
+        <v>29</v>
+      </c>
+      <c r="G147" t="s">
+        <v>159</v>
+      </c>
+      <c r="H147" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" t="s">
+        <v>18</v>
+      </c>
+      <c r="K147">
+        <v>100</v>
+      </c>
+      <c r="L147">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>19</v>
+      </c>
+      <c r="B148">
+        <v>4</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148" t="s">
+        <v>26</v>
+      </c>
+      <c r="E148" t="s">
+        <v>162</v>
+      </c>
+      <c r="F148" t="s">
+        <v>29</v>
+      </c>
+      <c r="G148" t="s">
+        <v>159</v>
+      </c>
+      <c r="H148" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148" t="s">
+        <v>18</v>
+      </c>
+      <c r="K148">
+        <v>100</v>
+      </c>
+      <c r="L148">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>21</v>
+      </c>
+      <c r="B149">
+        <v>42</v>
+      </c>
+      <c r="C149">
+        <v>39</v>
+      </c>
+      <c r="D149" t="s">
+        <v>62</v>
+      </c>
+      <c r="E149" t="s">
+        <v>162</v>
+      </c>
+      <c r="F149" t="s">
+        <v>29</v>
+      </c>
+      <c r="G149" t="s">
+        <v>159</v>
+      </c>
+      <c r="H149" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149" t="s">
+        <v>18</v>
+      </c>
+      <c r="K149">
+        <v>100</v>
+      </c>
+      <c r="L149">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>23</v>
+      </c>
+      <c r="B150">
+        <v>84</v>
+      </c>
+      <c r="C150">
+        <v>58</v>
+      </c>
+      <c r="D150" t="s">
+        <v>163</v>
+      </c>
+      <c r="E150" t="s">
+        <v>162</v>
+      </c>
+      <c r="F150" t="s">
+        <v>29</v>
+      </c>
+      <c r="G150" t="s">
+        <v>159</v>
+      </c>
+      <c r="H150" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150" t="s">
+        <v>18</v>
+      </c>
+      <c r="K150">
+        <v>100</v>
+      </c>
+      <c r="L150">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>25</v>
+      </c>
+      <c r="B151">
+        <v>900</v>
+      </c>
+      <c r="C151">
+        <v>789</v>
+      </c>
+      <c r="D151" t="s">
+        <v>100</v>
+      </c>
+      <c r="E151" t="s">
+        <v>162</v>
+      </c>
+      <c r="F151" t="s">
+        <v>29</v>
+      </c>
+      <c r="G151" t="s">
+        <v>159</v>
+      </c>
+      <c r="H151" t="s">
+        <v>17</v>
+      </c>
+      <c r="I151" t="s">
+        <v>18</v>
+      </c>
+      <c r="K151">
+        <v>100</v>
+      </c>
+      <c r="L151">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>12</v>
+      </c>
+      <c r="B152">
+        <v>21</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152" t="s">
+        <v>26</v>
+      </c>
+      <c r="E152" t="s">
+        <v>103</v>
+      </c>
+      <c r="F152" t="s">
+        <v>73</v>
+      </c>
+      <c r="G152" t="s">
+        <v>159</v>
+      </c>
+      <c r="H152" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152" t="s">
+        <v>18</v>
+      </c>
+      <c r="J152" t="s">
+        <v>164</v>
+      </c>
+      <c r="K152">
+        <v>100</v>
+      </c>
+      <c r="L152">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>19</v>
+      </c>
+      <c r="B153">
+        <v>4</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153" t="s">
+        <v>26</v>
+      </c>
+      <c r="E153" t="s">
+        <v>103</v>
+      </c>
+      <c r="F153" t="s">
+        <v>73</v>
+      </c>
+      <c r="G153" t="s">
+        <v>159</v>
+      </c>
+      <c r="H153" t="s">
+        <v>17</v>
+      </c>
+      <c r="I153" t="s">
+        <v>18</v>
+      </c>
+      <c r="J153" t="s">
+        <v>165</v>
+      </c>
+      <c r="K153">
+        <v>100</v>
+      </c>
+      <c r="L153">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>21</v>
+      </c>
+      <c r="B154">
+        <v>42</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154" t="s">
+        <v>26</v>
+      </c>
+      <c r="E154" t="s">
+        <v>103</v>
+      </c>
+      <c r="F154" t="s">
+        <v>73</v>
+      </c>
+      <c r="G154" t="s">
+        <v>159</v>
+      </c>
+      <c r="H154" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154" t="s">
+        <v>18</v>
+      </c>
+      <c r="J154" t="s">
+        <v>166</v>
+      </c>
+      <c r="K154">
+        <v>100</v>
+      </c>
+      <c r="L154">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>23</v>
+      </c>
+      <c r="B155">
+        <v>84</v>
+      </c>
+      <c r="C155">
+        <v>3</v>
+      </c>
+      <c r="D155" t="s">
+        <v>167</v>
+      </c>
+      <c r="E155" t="s">
+        <v>103</v>
+      </c>
+      <c r="F155" t="s">
+        <v>73</v>
+      </c>
+      <c r="G155" t="s">
+        <v>159</v>
+      </c>
+      <c r="H155" t="s">
+        <v>17</v>
+      </c>
+      <c r="I155" t="s">
+        <v>18</v>
+      </c>
+      <c r="J155" t="s">
+        <v>168</v>
+      </c>
+      <c r="K155">
+        <v>100</v>
+      </c>
+      <c r="L155">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>25</v>
+      </c>
+      <c r="B156">
+        <v>900</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156" t="s">
+        <v>26</v>
+      </c>
+      <c r="E156" t="s">
+        <v>103</v>
+      </c>
+      <c r="F156" t="s">
+        <v>73</v>
+      </c>
+      <c r="G156" t="s">
+        <v>159</v>
+      </c>
+      <c r="H156" t="s">
+        <v>17</v>
+      </c>
+      <c r="I156" t="s">
+        <v>18</v>
+      </c>
+      <c r="K156">
+        <v>100</v>
+      </c>
+      <c r="L156">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>12</v>
+      </c>
+      <c r="B157">
+        <v>14</v>
+      </c>
+      <c r="C157">
+        <v>16</v>
+      </c>
+      <c r="D157" t="s">
+        <v>127</v>
+      </c>
+      <c r="E157" t="s">
+        <v>169</v>
+      </c>
+      <c r="F157" t="s">
+        <v>15</v>
+      </c>
+      <c r="G157" t="s">
+        <v>170</v>
+      </c>
+      <c r="H157" t="s">
+        <v>17</v>
+      </c>
+      <c r="I157" t="s">
+        <v>18</v>
+      </c>
+      <c r="K157">
+        <v>100</v>
+      </c>
+      <c r="L157">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>19</v>
+      </c>
+      <c r="B158">
+        <v>3</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158" t="s">
+        <v>36</v>
+      </c>
+      <c r="E158" t="s">
+        <v>169</v>
+      </c>
+      <c r="F158" t="s">
+        <v>15</v>
+      </c>
+      <c r="G158" t="s">
+        <v>170</v>
+      </c>
+      <c r="H158" t="s">
+        <v>17</v>
+      </c>
+      <c r="I158" t="s">
+        <v>18</v>
+      </c>
+      <c r="K158">
+        <v>100</v>
+      </c>
+      <c r="L158">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>21</v>
+      </c>
+      <c r="B159">
         <v>20</v>
       </c>
-      <c r="B106">
-        <v>305</v>
-      </c>
-      <c r="C106">
+      <c r="C159">
+        <v>24</v>
+      </c>
+      <c r="D159" t="s">
+        <v>40</v>
+      </c>
+      <c r="E159" t="s">
+        <v>169</v>
+      </c>
+      <c r="F159" t="s">
+        <v>15</v>
+      </c>
+      <c r="G159" t="s">
+        <v>170</v>
+      </c>
+      <c r="H159" t="s">
+        <v>17</v>
+      </c>
+      <c r="I159" t="s">
+        <v>18</v>
+      </c>
+      <c r="K159">
+        <v>100</v>
+      </c>
+      <c r="L159">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>23</v>
+      </c>
+      <c r="B160">
+        <v>52</v>
+      </c>
+      <c r="C160">
+        <v>52</v>
+      </c>
+      <c r="D160" t="s">
+        <v>27</v>
+      </c>
+      <c r="E160" t="s">
+        <v>169</v>
+      </c>
+      <c r="F160" t="s">
+        <v>15</v>
+      </c>
+      <c r="G160" t="s">
+        <v>170</v>
+      </c>
+      <c r="H160" t="s">
+        <v>17</v>
+      </c>
+      <c r="I160" t="s">
+        <v>18</v>
+      </c>
+      <c r="K160">
+        <v>100</v>
+      </c>
+      <c r="L160">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>25</v>
+      </c>
+      <c r="B161">
+        <v>480</v>
+      </c>
+      <c r="C161">
+        <v>481</v>
+      </c>
+      <c r="D161" t="s">
+        <v>27</v>
+      </c>
+      <c r="E161" t="s">
+        <v>169</v>
+      </c>
+      <c r="F161" t="s">
+        <v>15</v>
+      </c>
+      <c r="G161" t="s">
+        <v>170</v>
+      </c>
+      <c r="H161" t="s">
+        <v>17</v>
+      </c>
+      <c r="I161" t="s">
+        <v>18</v>
+      </c>
+      <c r="K161">
+        <v>100</v>
+      </c>
+      <c r="L161">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>12</v>
+      </c>
+      <c r="B162">
+        <v>21</v>
+      </c>
+      <c r="C162">
+        <v>20</v>
+      </c>
+      <c r="D162" t="s">
+        <v>125</v>
+      </c>
+      <c r="E162" t="s">
+        <v>171</v>
+      </c>
+      <c r="F162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G162" t="s">
+        <v>170</v>
+      </c>
+      <c r="H162" t="s">
+        <v>17</v>
+      </c>
+      <c r="I162" t="s">
+        <v>18</v>
+      </c>
+      <c r="K162">
+        <v>100</v>
+      </c>
+      <c r="L162">
+        <v>103.2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>19</v>
+      </c>
+      <c r="B163">
+        <v>5</v>
+      </c>
+      <c r="C163">
+        <v>2</v>
+      </c>
+      <c r="D163" t="s">
+        <v>20</v>
+      </c>
+      <c r="E163" t="s">
+        <v>171</v>
+      </c>
+      <c r="F163" t="s">
+        <v>29</v>
+      </c>
+      <c r="G163" t="s">
+        <v>170</v>
+      </c>
+      <c r="H163" t="s">
+        <v>17</v>
+      </c>
+      <c r="I163" t="s">
+        <v>18</v>
+      </c>
+      <c r="K163">
+        <v>100</v>
+      </c>
+      <c r="L163">
+        <v>103.2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>21</v>
+      </c>
+      <c r="B164">
+        <v>30</v>
+      </c>
+      <c r="C164">
+        <v>36</v>
+      </c>
+      <c r="D164" t="s">
+        <v>40</v>
+      </c>
+      <c r="E164" t="s">
+        <v>171</v>
+      </c>
+      <c r="F164" t="s">
+        <v>29</v>
+      </c>
+      <c r="G164" t="s">
+        <v>170</v>
+      </c>
+      <c r="H164" t="s">
+        <v>17</v>
+      </c>
+      <c r="I164" t="s">
+        <v>18</v>
+      </c>
+      <c r="K164">
+        <v>100</v>
+      </c>
+      <c r="L164">
+        <v>103.2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>23</v>
+      </c>
+      <c r="B165">
+        <v>78</v>
+      </c>
+      <c r="C165">
+        <v>84</v>
+      </c>
+      <c r="D165" t="s">
+        <v>101</v>
+      </c>
+      <c r="E165" t="s">
+        <v>171</v>
+      </c>
+      <c r="F165" t="s">
+        <v>29</v>
+      </c>
+      <c r="G165" t="s">
+        <v>170</v>
+      </c>
+      <c r="H165" t="s">
+        <v>17</v>
+      </c>
+      <c r="I165" t="s">
+        <v>18</v>
+      </c>
+      <c r="K165">
+        <v>100</v>
+      </c>
+      <c r="L165">
+        <v>103.2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>25</v>
+      </c>
+      <c r="B166">
+        <v>720</v>
+      </c>
+      <c r="C166">
+        <v>731</v>
+      </c>
+      <c r="D166" t="s">
+        <v>156</v>
+      </c>
+      <c r="E166" t="s">
+        <v>171</v>
+      </c>
+      <c r="F166" t="s">
+        <v>29</v>
+      </c>
+      <c r="G166" t="s">
+        <v>170</v>
+      </c>
+      <c r="H166" t="s">
+        <v>17</v>
+      </c>
+      <c r="I166" t="s">
+        <v>18</v>
+      </c>
+      <c r="K166">
+        <v>100</v>
+      </c>
+      <c r="L166">
+        <v>103.2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>12</v>
+      </c>
+      <c r="B167">
+        <v>930</v>
+      </c>
+      <c r="C167">
+        <v>4</v>
+      </c>
+      <c r="D167" t="s">
+        <v>26</v>
+      </c>
+      <c r="E167" t="s">
+        <v>103</v>
+      </c>
+      <c r="F167" t="s">
+        <v>15</v>
+      </c>
+      <c r="G167" t="s">
+        <v>172</v>
+      </c>
+      <c r="H167" t="s">
+        <v>17</v>
+      </c>
+      <c r="I167" t="s">
+        <v>18</v>
+      </c>
+      <c r="J167" t="s">
+        <v>173</v>
+      </c>
+      <c r="K167">
+        <v>100</v>
+      </c>
+      <c r="L167">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>19</v>
+      </c>
+      <c r="B168">
+        <v>156</v>
+      </c>
+      <c r="C168">
         <v>0</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D168" t="s">
+        <v>26</v>
+      </c>
+      <c r="E168" t="s">
+        <v>103</v>
+      </c>
+      <c r="F168" t="s">
+        <v>15</v>
+      </c>
+      <c r="G168" t="s">
+        <v>172</v>
+      </c>
+      <c r="H168" t="s">
+        <v>17</v>
+      </c>
+      <c r="I168" t="s">
+        <v>18</v>
+      </c>
+      <c r="J168" t="s">
+        <v>174</v>
+      </c>
+      <c r="K168">
+        <v>100</v>
+      </c>
+      <c r="L168">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>21</v>
       </c>
-      <c r="E106" t="s">
-        <v>63</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="B169">
+        <v>1712</v>
+      </c>
+      <c r="C169">
+        <v>3</v>
+      </c>
+      <c r="D169" t="s">
+        <v>26</v>
+      </c>
+      <c r="E169" t="s">
+        <v>103</v>
+      </c>
+      <c r="F169" t="s">
+        <v>15</v>
+      </c>
+      <c r="G169" t="s">
+        <v>172</v>
+      </c>
+      <c r="H169" t="s">
+        <v>17</v>
+      </c>
+      <c r="I169" t="s">
+        <v>18</v>
+      </c>
+      <c r="J169" t="s">
+        <v>175</v>
+      </c>
+      <c r="K169">
+        <v>100</v>
+      </c>
+      <c r="L169">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
         <v>23</v>
       </c>
-      <c r="G106" t="s">
-        <v>62</v>
-      </c>
-      <c r="H106" t="s">
-        <v>36</v>
-      </c>
-      <c r="I106" t="s">
-        <v>16</v>
-      </c>
-      <c r="K106">
-        <v>100</v>
-      </c>
-      <c r="L106">
-        <v>116</v>
+      <c r="B170">
+        <v>3255</v>
+      </c>
+      <c r="C170">
+        <v>24</v>
+      </c>
+      <c r="D170" t="s">
+        <v>176</v>
+      </c>
+      <c r="E170" t="s">
+        <v>103</v>
+      </c>
+      <c r="F170" t="s">
+        <v>15</v>
+      </c>
+      <c r="G170" t="s">
+        <v>172</v>
+      </c>
+      <c r="H170" t="s">
+        <v>17</v>
+      </c>
+      <c r="I170" t="s">
+        <v>18</v>
+      </c>
+      <c r="J170" t="s">
+        <v>177</v>
+      </c>
+      <c r="K170">
+        <v>100</v>
+      </c>
+      <c r="L170">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B171">
+        <v>27700</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171" t="s">
+        <v>26</v>
+      </c>
+      <c r="E171" t="s">
+        <v>103</v>
+      </c>
+      <c r="F171" t="s">
+        <v>15</v>
+      </c>
+      <c r="G171" t="s">
+        <v>172</v>
+      </c>
+      <c r="H171" t="s">
+        <v>17</v>
+      </c>
+      <c r="I171" t="s">
+        <v>18</v>
+      </c>
+      <c r="K171">
+        <v>100</v>
+      </c>
+      <c r="L171">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>12</v>
+      </c>
+      <c r="B172">
+        <v>930</v>
+      </c>
+      <c r="C172">
+        <v>14</v>
+      </c>
+      <c r="D172" t="s">
+        <v>81</v>
+      </c>
+      <c r="E172" t="s">
+        <v>76</v>
+      </c>
+      <c r="F172" t="s">
+        <v>73</v>
+      </c>
+      <c r="G172" t="s">
+        <v>172</v>
+      </c>
+      <c r="H172" t="s">
+        <v>17</v>
+      </c>
+      <c r="I172" t="s">
+        <v>18</v>
+      </c>
+      <c r="J172" t="s">
+        <v>178</v>
+      </c>
+      <c r="K172">
+        <v>100</v>
+      </c>
+      <c r="L172">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>19</v>
+      </c>
+      <c r="B173">
+        <v>156</v>
+      </c>
+      <c r="C173">
+        <v>2</v>
+      </c>
+      <c r="D173" t="s">
+        <v>176</v>
+      </c>
+      <c r="E173" t="s">
+        <v>76</v>
+      </c>
+      <c r="F173" t="s">
+        <v>73</v>
+      </c>
+      <c r="G173" t="s">
+        <v>172</v>
+      </c>
+      <c r="H173" t="s">
+        <v>17</v>
+      </c>
+      <c r="I173" t="s">
+        <v>18</v>
+      </c>
+      <c r="J173" t="s">
+        <v>179</v>
+      </c>
+      <c r="K173">
+        <v>100</v>
+      </c>
+      <c r="L173">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>21</v>
+      </c>
+      <c r="B174">
+        <v>1712</v>
+      </c>
+      <c r="C174">
+        <v>19</v>
+      </c>
+      <c r="D174" t="s">
+        <v>176</v>
+      </c>
+      <c r="E174" t="s">
+        <v>76</v>
+      </c>
+      <c r="F174" t="s">
+        <v>73</v>
+      </c>
+      <c r="G174" t="s">
+        <v>172</v>
+      </c>
+      <c r="H174" t="s">
+        <v>17</v>
+      </c>
+      <c r="I174" t="s">
+        <v>18</v>
+      </c>
+      <c r="J174" t="s">
+        <v>180</v>
+      </c>
+      <c r="K174">
+        <v>100</v>
+      </c>
+      <c r="L174">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>23</v>
+      </c>
+      <c r="B175">
+        <v>3255</v>
+      </c>
+      <c r="C175">
+        <v>38</v>
+      </c>
+      <c r="D175" t="s">
+        <v>176</v>
+      </c>
+      <c r="E175" t="s">
+        <v>76</v>
+      </c>
+      <c r="F175" t="s">
+        <v>73</v>
+      </c>
+      <c r="G175" t="s">
+        <v>172</v>
+      </c>
+      <c r="H175" t="s">
+        <v>17</v>
+      </c>
+      <c r="I175" t="s">
+        <v>18</v>
+      </c>
+      <c r="K175">
+        <v>100</v>
+      </c>
+      <c r="L175">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>25</v>
+      </c>
+      <c r="B176">
+        <v>27700</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+      <c r="D176" t="s">
+        <v>26</v>
+      </c>
+      <c r="E176" t="s">
+        <v>76</v>
+      </c>
+      <c r="F176" t="s">
+        <v>73</v>
+      </c>
+      <c r="G176" t="s">
+        <v>172</v>
+      </c>
+      <c r="H176" t="s">
+        <v>17</v>
+      </c>
+      <c r="I176" t="s">
+        <v>18</v>
+      </c>
+      <c r="K176">
+        <v>100</v>
+      </c>
+      <c r="L176">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
